--- a/data/data_france.xlsx
+++ b/data/data_france.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6468b3e9d8abaf9d/MQDE/S2/ESSD/Projet/ESSD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{EA4EE90D-5F88-5A42-910A-B6446A619315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0E22BF1-A939-435F-8491-5275B502E426}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{EA4EE90D-5F88-5A42-910A-B6446A619315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEF5C451-5465-49BF-964E-7B19C5581C9C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{92925F57-A0AC-404C-B2CD-8ED23E7BB18B}"/>
+    <workbookView xWindow="0" yWindow="10" windowWidth="19190" windowHeight="10070" activeTab="1" xr2:uid="{92925F57-A0AC-404C-B2CD-8ED23E7BB18B}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenues" sheetId="1" r:id="rId1"/>
@@ -15118,6 +15118,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D49BF3C-99BE-B04B-9A3C-656750B962CB}">
   <dimension ref="A1:Q313"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="11.9140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">

--- a/data/data_france.xlsx
+++ b/data/data_france.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6468b3e9d8abaf9d/MQDE/S2/ESSD/Projet/ESSD/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timotheedangleterre/Desktop/ENSAE/Semestre 1/ESSD/ProjetESSD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{EA4EE90D-5F88-5A42-910A-B6446A619315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0E22BF1-A939-435F-8491-5275B502E426}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A069E3-2687-8E43-8564-AE3A5DA5E0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{92925F57-A0AC-404C-B2CD-8ED23E7BB18B}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27180" windowHeight="15540" xr2:uid="{92925F57-A0AC-404C-B2CD-8ED23E7BB18B}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenues" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,6 @@
     <author>tc={7C05136F-F1F6-1B48-A0FD-D9948482DAB4}</author>
     <author>tc={21B6A951-F9DD-EA4D-BBDB-1E84C1701EAC}</author>
     <author>tc={F2FC6E49-4445-9F42-A24F-41F47EAE24C1}</author>
-    <author>tc={0D899E68-CBC0-3C4E-A882-E37DCF27B76E}</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{78C80B45-7F86-1D48-845D-369F96715558}">
@@ -122,14 +121,6 @@
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     Yahoo finance log returns</t>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="8" shapeId="0" xr:uid="{0D899E68-CBC0-3C4E-A882-E37DCF27B76E}">
-      <text>
-        <t>[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    DBnomics</t>
       </text>
     </comment>
   </commentList>
@@ -260,7 +251,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="43">
   <si>
     <t>Dates</t>
   </si>
@@ -305,9 +296,6 @@
   </si>
   <si>
     <t xml:space="preserve">Stock market </t>
-  </si>
-  <si>
-    <t>Consumer confidence</t>
   </si>
   <si>
     <t>Total expenditure</t>
@@ -917,9 +905,6 @@
   <threadedComment ref="O1" dT="2026-02-09T16:46:20.14" personId="{E0F60C48-9375-0B4A-8578-0334C1C9071A}" id="{F2FC6E49-4445-9F42-A24F-41F47EAE24C1}">
     <text>Yahoo finance log returns</text>
   </threadedComment>
-  <threadedComment ref="P1" dT="2026-02-09T16:16:35.84" personId="{E0F60C48-9375-0B4A-8578-0334C1C9071A}" id="{0D899E68-CBC0-3C4E-A882-E37DCF27B76E}">
-    <text>DBnomics</text>
-  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -1012,10 +997,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCC83A82-CE31-B84F-BDF7-6A55FA66BF4B}">
-  <dimension ref="A1:Q314"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:O314"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1061,11 +1046,8 @@
       <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>36526</v>
       </c>
@@ -1102,15 +1084,8 @@
       <c r="O2">
         <v>8.9699824115209395E-2</v>
       </c>
-      <c r="P2">
-        <v>-1.4</v>
-      </c>
-      <c r="Q2" t="str">
-        <f>IF(MONTH($A2) = 1, YEAR($A2)&amp;"-Q"&amp;MONTH($A2), IF(MONTH($A2) = 4, YEAR($A2)&amp;"-Q2", IF(MONTH($A2) = 7, YEAR($A2)&amp;"-Q3", IF(MONTH($A2) = 10, YEAR($A2)&amp;"-Q4",""))))</f>
-        <v>2000-Q1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>36557</v>
       </c>
@@ -1147,15 +1122,8 @@
       <c r="O3">
         <v>1.5242704242000501E-2</v>
       </c>
-      <c r="P3">
-        <v>-1.8</v>
-      </c>
-      <c r="Q3" t="str">
-        <f t="shared" ref="Q3:Q66" si="0">IF(MONTH($A3) = 1, YEAR($A3)&amp;"-Q"&amp;MONTH($A3), IF(MONTH($A3) = 4, YEAR($A3)&amp;"-Q2", IF(MONTH($A3) = 7, YEAR($A3)&amp;"-Q3", IF(MONTH($A3) = 10, YEAR($A3)&amp;"-Q4",""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>36586</v>
       </c>
@@ -1192,15 +1160,8 @@
       <c r="O4">
         <v>2.1041675052957801E-2</v>
       </c>
-      <c r="P4">
-        <v>-1</v>
-      </c>
-      <c r="Q4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>36617</v>
       </c>
@@ -1237,15 +1198,8 @@
       <c r="O5">
         <v>1.01814752258989E-3</v>
       </c>
-      <c r="P5">
-        <v>0.1</v>
-      </c>
-      <c r="Q5" t="str">
-        <f t="shared" si="0"/>
-        <v>2000-Q2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>36647</v>
       </c>
@@ -1282,15 +1236,8 @@
       <c r="O6">
         <v>3.15087479394727E-3</v>
       </c>
-      <c r="P6">
-        <v>-0.1</v>
-      </c>
-      <c r="Q6" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>36678</v>
       </c>
@@ -1327,15 +1274,8 @@
       <c r="O7">
         <v>1.47743039504462E-2</v>
       </c>
-      <c r="P7">
-        <v>-0.1</v>
-      </c>
-      <c r="Q7" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>36708</v>
       </c>
@@ -1372,15 +1312,8 @@
       <c r="O8">
         <v>1.2595891520739101E-2</v>
       </c>
-      <c r="P8">
-        <v>1.2</v>
-      </c>
-      <c r="Q8" t="str">
-        <f t="shared" si="0"/>
-        <v>2000-Q3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>36739</v>
       </c>
@@ -1417,15 +1350,8 @@
       <c r="O9">
         <v>-5.5675042910936098E-2</v>
       </c>
-      <c r="P9">
-        <v>-0.9</v>
-      </c>
-      <c r="Q9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>36770</v>
       </c>
@@ -1462,15 +1388,8 @@
       <c r="O10">
         <v>2.0693611544897898E-2</v>
       </c>
-      <c r="P10">
-        <v>-3.1</v>
-      </c>
-      <c r="Q10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>36800</v>
       </c>
@@ -1507,15 +1426,8 @@
       <c r="O11">
         <v>-7.62319265733193E-2</v>
       </c>
-      <c r="P11">
-        <v>-0.8</v>
-      </c>
-      <c r="Q11" t="str">
-        <f t="shared" si="0"/>
-        <v>2000-Q4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>36831</v>
       </c>
@@ -1552,15 +1464,8 @@
       <c r="O12">
         <v>-2.8008878668117599E-4</v>
       </c>
-      <c r="P12">
-        <v>-0.7</v>
-      </c>
-      <c r="Q12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>36861</v>
       </c>
@@ -1597,15 +1502,8 @@
       <c r="O13">
         <v>1.20875023888498E-2</v>
       </c>
-      <c r="P13">
-        <v>1.3</v>
-      </c>
-      <c r="Q13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>36892</v>
       </c>
@@ -1642,15 +1540,8 @@
       <c r="O14">
         <v>-0.111149288964787</v>
       </c>
-      <c r="P14">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="str">
-        <f t="shared" si="0"/>
-        <v>2001-Q1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>36923</v>
       </c>
@@ -1687,15 +1578,8 @@
       <c r="O15">
         <v>-3.5466558208662798E-2</v>
       </c>
-      <c r="P15">
-        <v>0.5</v>
-      </c>
-      <c r="Q15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>36951</v>
       </c>
@@ -1732,15 +1616,8 @@
       <c r="O16">
         <v>8.4997383765195195E-2</v>
       </c>
-      <c r="P16">
-        <v>-0.8</v>
-      </c>
-      <c r="Q16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>36982</v>
       </c>
@@ -1777,15 +1654,8 @@
       <c r="O17">
         <v>-3.3505236661358899E-2</v>
       </c>
-      <c r="P17">
-        <v>-1.5</v>
-      </c>
-      <c r="Q17" t="str">
-        <f t="shared" si="0"/>
-        <v>2001-Q2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>37012</v>
       </c>
@@ -1822,15 +1692,8 @@
       <c r="O18">
         <v>-4.28661411882914E-2</v>
       </c>
-      <c r="P18">
-        <v>-4.7</v>
-      </c>
-      <c r="Q18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>37043</v>
       </c>
@@ -1867,15 +1730,8 @@
       <c r="O19">
         <v>-2.7122695332700199E-2</v>
       </c>
-      <c r="P19">
-        <v>-4.8</v>
-      </c>
-      <c r="Q19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>37073</v>
       </c>
@@ -1912,15 +1768,8 @@
       <c r="O20">
         <v>-8.1103459081191404E-2</v>
       </c>
-      <c r="P20">
-        <v>-4.7</v>
-      </c>
-      <c r="Q20" t="str">
-        <f t="shared" si="0"/>
-        <v>2001-Q3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>37104</v>
       </c>
@@ -1957,15 +1806,8 @@
       <c r="O21">
         <v>-0.139435046014391</v>
       </c>
-      <c r="P21">
-        <v>-6.1</v>
-      </c>
-      <c r="Q21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>37135</v>
       </c>
@@ -2002,15 +1844,8 @@
       <c r="O22">
         <v>6.2314779693515697E-2</v>
       </c>
-      <c r="P22">
-        <v>-7.6</v>
-      </c>
-      <c r="Q22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>37165</v>
       </c>
@@ -2047,15 +1882,8 @@
       <c r="O23">
         <v>3.0571660308368099E-2</v>
       </c>
-      <c r="P23">
-        <v>-6.5</v>
-      </c>
-      <c r="Q23" t="str">
-        <f t="shared" si="0"/>
-        <v>2001-Q4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>37196</v>
       </c>
@@ -2092,15 +1920,8 @@
       <c r="O24">
         <v>3.2642364647406601E-2</v>
       </c>
-      <c r="P24">
-        <v>-5</v>
-      </c>
-      <c r="Q24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>37226</v>
       </c>
@@ -2137,15 +1958,8 @@
       <c r="O25">
         <v>-3.5817585990407998E-2</v>
       </c>
-      <c r="P25">
-        <v>-4.0999999999999996</v>
-      </c>
-      <c r="Q25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>37257</v>
       </c>
@@ -2182,15 +1996,8 @@
       <c r="O26">
         <v>2.51010581513E-4</v>
       </c>
-      <c r="P26">
-        <v>-4</v>
-      </c>
-      <c r="Q26" t="str">
-        <f t="shared" si="0"/>
-        <v>2002-Q1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>37288</v>
       </c>
@@ -2227,15 +2034,8 @@
       <c r="O27">
         <v>4.9191325128862901E-2</v>
       </c>
-      <c r="P27">
-        <v>-3.9</v>
-      </c>
-      <c r="Q27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>37316</v>
       </c>
@@ -2272,15 +2072,8 @@
       <c r="O28">
         <v>-4.9247342953048397E-2</v>
       </c>
-      <c r="P28">
-        <v>-3.8</v>
-      </c>
-      <c r="Q28" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>37347</v>
       </c>
@@ -2317,15 +2110,8 @@
       <c r="O29">
         <v>-4.3063059390183497E-2</v>
       </c>
-      <c r="P29">
-        <v>-5.5</v>
-      </c>
-      <c r="Q29" t="str">
-        <f t="shared" si="0"/>
-        <v>2002-Q2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>37377</v>
       </c>
@@ -2362,15 +2148,8 @@
       <c r="O30">
         <v>-9.2238887141570899E-2</v>
       </c>
-      <c r="P30">
-        <v>-2.2000000000000002</v>
-      </c>
-      <c r="Q30" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>37408</v>
       </c>
@@ -2407,15 +2186,8 @@
       <c r="O31">
         <v>-0.132172306845943</v>
       </c>
-      <c r="P31">
-        <v>-3</v>
-      </c>
-      <c r="Q31" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>37438</v>
       </c>
@@ -2452,15 +2224,8 @@
       <c r="O32">
         <v>-1.4501255502644E-2</v>
       </c>
-      <c r="P32">
-        <v>-4.3</v>
-      </c>
-      <c r="Q32" t="str">
-        <f t="shared" si="0"/>
-        <v>2002-Q3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>37469</v>
       </c>
@@ -2497,15 +2262,8 @@
       <c r="O33">
         <v>-0.192254247820797</v>
       </c>
-      <c r="P33">
-        <v>-5.4</v>
-      </c>
-      <c r="Q33" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>37500</v>
       </c>
@@ -2542,15 +2300,8 @@
       <c r="O34">
         <v>0.12588194058101901</v>
       </c>
-      <c r="P34">
-        <v>-6.7</v>
-      </c>
-      <c r="Q34" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>37530</v>
       </c>
@@ -2587,15 +2338,8 @@
       <c r="O35">
         <v>5.4550598696685902E-2</v>
       </c>
-      <c r="P35">
-        <v>-5.3</v>
-      </c>
-      <c r="Q35" t="str">
-        <f t="shared" si="0"/>
-        <v>2002-Q4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>37561</v>
       </c>
@@ -2632,15 +2376,8 @@
       <c r="O36">
         <v>-8.22739128739194E-2</v>
       </c>
-      <c r="P36">
-        <v>-5.0999999999999996</v>
-      </c>
-      <c r="Q36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>37591</v>
       </c>
@@ -2677,15 +2414,8 @@
       <c r="O37">
         <v>-4.2003656475575503E-2</v>
       </c>
-      <c r="P37">
-        <v>-4.4000000000000004</v>
-      </c>
-      <c r="Q37" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>37622</v>
       </c>
@@ -2722,15 +2452,8 @@
       <c r="O38">
         <v>-6.4608350538345696E-2</v>
       </c>
-      <c r="P38">
-        <v>-6.7</v>
-      </c>
-      <c r="Q38" t="str">
-        <f t="shared" si="0"/>
-        <v>2003-Q1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>37653</v>
       </c>
@@ -2767,15 +2490,8 @@
       <c r="O39">
         <v>-5.0493498597819403E-2</v>
       </c>
-      <c r="P39">
-        <v>-9.1</v>
-      </c>
-      <c r="Q39" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>37681</v>
       </c>
@@ -2812,15 +2528,8 @@
       <c r="O40">
         <v>0.120462094705792</v>
       </c>
-      <c r="P40">
-        <v>-11.4</v>
-      </c>
-      <c r="Q40" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>37712</v>
       </c>
@@ -2857,15 +2566,8 @@
       <c r="O41">
         <v>1.2810061984417601E-2</v>
       </c>
-      <c r="P41">
-        <v>-10.1</v>
-      </c>
-      <c r="Q41" t="str">
-        <f t="shared" si="0"/>
-        <v>2003-Q2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>37742</v>
       </c>
@@ -2902,15 +2604,8 @@
       <c r="O42">
         <v>3.0401411789856801E-2</v>
       </c>
-      <c r="P42">
-        <v>-10.1</v>
-      </c>
-      <c r="Q42" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>37773</v>
       </c>
@@ -2947,15 +2642,8 @@
       <c r="O43">
         <v>4.0095139576873599E-2</v>
       </c>
-      <c r="P43">
-        <v>-10</v>
-      </c>
-      <c r="Q43" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>37803</v>
       </c>
@@ -2992,15 +2680,8 @@
       <c r="O44">
         <v>3.10220249838178E-2</v>
       </c>
-      <c r="P44">
-        <v>-9.6</v>
-      </c>
-      <c r="Q44" t="str">
-        <f t="shared" si="0"/>
-        <v>2003-Q3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>37834</v>
       </c>
@@ -3037,15 +2718,8 @@
       <c r="O45">
         <v>-5.4751095649944397E-2</v>
       </c>
-      <c r="P45">
-        <v>-10.1</v>
-      </c>
-      <c r="Q45" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>37865</v>
       </c>
@@ -3082,15 +2756,8 @@
       <c r="O46">
         <v>7.3235853070945794E-2</v>
       </c>
-      <c r="P46">
-        <v>-10.8</v>
-      </c>
-      <c r="Q46" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>37895</v>
       </c>
@@ -3127,15 +2794,8 @@
       <c r="O47">
         <v>1.51783331285742E-2</v>
       </c>
-      <c r="P47">
-        <v>-10</v>
-      </c>
-      <c r="Q47" t="str">
-        <f t="shared" si="0"/>
-        <v>2003-Q4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>37926</v>
       </c>
@@ -3172,15 +2832,8 @@
       <c r="O48">
         <v>3.8130288351990102E-2</v>
       </c>
-      <c r="P48">
-        <v>-9.6999999999999993</v>
-      </c>
-      <c r="Q48" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>37956</v>
       </c>
@@ -3217,15 +2870,8 @@
       <c r="O49">
         <v>2.23845465294072E-2</v>
       </c>
-      <c r="P49">
-        <v>-8.8000000000000007</v>
-      </c>
-      <c r="Q49" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>37987</v>
       </c>
@@ -3262,15 +2908,8 @@
       <c r="O50">
         <v>2.3629947680161599E-2</v>
       </c>
-      <c r="P50">
-        <v>-6.2</v>
-      </c>
-      <c r="Q50" t="str">
-        <f t="shared" si="0"/>
-        <v>2004-Q1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>38018</v>
       </c>
@@ -3307,15 +2946,8 @@
       <c r="O51">
         <v>-2.72672207510158E-2</v>
       </c>
-      <c r="P51">
-        <v>-7</v>
-      </c>
-      <c r="Q51" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>38047</v>
       </c>
@@ -3352,15 +2984,8 @@
       <c r="O52">
         <v>1.34394738942891E-2</v>
       </c>
-      <c r="P52">
-        <v>-7.1</v>
-      </c>
-      <c r="Q52" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>38078</v>
       </c>
@@ -3397,15 +3022,8 @@
       <c r="O53">
         <v>-1.26639546549612E-3</v>
       </c>
-      <c r="P53">
-        <v>-9.6999999999999993</v>
-      </c>
-      <c r="Q53" t="str">
-        <f t="shared" si="0"/>
-        <v>2004-Q2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>38108</v>
       </c>
@@ -3442,15 +3060,8 @@
       <c r="O54">
         <v>1.7118710891269401E-2</v>
       </c>
-      <c r="P54">
-        <v>-8.1</v>
-      </c>
-      <c r="Q54" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>38139</v>
       </c>
@@ -3487,15 +3098,8 @@
       <c r="O55">
         <v>-2.32771604780844E-2</v>
       </c>
-      <c r="P55">
-        <v>-8.4</v>
-      </c>
-      <c r="Q55" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>38169</v>
       </c>
@@ -3532,15 +3136,8 @@
       <c r="O56">
         <v>-1.45886569226175E-2</v>
       </c>
-      <c r="P56">
-        <v>-7.9</v>
-      </c>
-      <c r="Q56" t="str">
-        <f t="shared" si="0"/>
-        <v>2004-Q3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>38200</v>
       </c>
@@ -3577,15 +3174,8 @@
       <c r="O57">
         <v>1.28075784309107E-2</v>
       </c>
-      <c r="P57">
-        <v>-7.5</v>
-      </c>
-      <c r="Q57" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>38231</v>
       </c>
@@ -3622,15 +3212,8 @@
       <c r="O58">
         <v>1.8023105114302499E-2</v>
       </c>
-      <c r="P58">
-        <v>-7.2</v>
-      </c>
-      <c r="Q58" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>38261</v>
       </c>
@@ -3667,15 +3250,8 @@
       <c r="O59">
         <v>1.25809556686747E-2</v>
       </c>
-      <c r="P59">
-        <v>-6.5</v>
-      </c>
-      <c r="Q59" t="str">
-        <f t="shared" si="0"/>
-        <v>2004-Q4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <v>38292</v>
       </c>
@@ -3712,15 +3288,8 @@
       <c r="O60">
         <v>1.7798678126654401E-2</v>
       </c>
-      <c r="P60">
-        <v>-8</v>
-      </c>
-      <c r="Q60" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <v>38322</v>
       </c>
@@ -3757,15 +3326,8 @@
       <c r="O61">
         <v>2.39266295621068E-2</v>
       </c>
-      <c r="P61">
-        <v>-6.9</v>
-      </c>
-      <c r="Q61" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>38353</v>
       </c>
@@ -3802,15 +3364,8 @@
       <c r="O62">
         <v>2.85807430616778E-2</v>
       </c>
-      <c r="P62">
-        <v>-8.3000000000000007</v>
-      </c>
-      <c r="Q62" t="str">
-        <f t="shared" si="0"/>
-        <v>2005-Q1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <v>38384</v>
       </c>
@@ -3847,15 +3402,8 @@
       <c r="O63">
         <v>1.00360122309375E-2</v>
       </c>
-      <c r="P63">
-        <v>-7.9</v>
-      </c>
-      <c r="Q63" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>38412</v>
       </c>
@@ -3892,15 +3440,8 @@
       <c r="O64">
         <v>-3.9122794737425103E-2</v>
       </c>
-      <c r="P64">
-        <v>-7.4</v>
-      </c>
-      <c r="Q64" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>38443</v>
       </c>
@@ -3937,15 +3478,8 @@
       <c r="O65">
         <v>5.2055718833031499E-2</v>
       </c>
-      <c r="P65">
-        <v>-10.199999999999999</v>
-      </c>
-      <c r="Q65" t="str">
-        <f t="shared" si="0"/>
-        <v>2005-Q2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
         <v>38473</v>
       </c>
@@ -3982,15 +3516,8 @@
       <c r="O66">
         <v>2.6018012645764099E-2</v>
       </c>
-      <c r="P66">
-        <v>-13</v>
-      </c>
-      <c r="Q66" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>38504</v>
       </c>
@@ -4027,15 +3554,8 @@
       <c r="O67">
         <v>5.1246743598934302E-2</v>
       </c>
-      <c r="P67">
-        <v>-8.9</v>
-      </c>
-      <c r="Q67" t="str">
-        <f t="shared" ref="Q67:Q130" si="1">IF(MONTH($A67) = 1, YEAR($A67)&amp;"-Q"&amp;MONTH($A67), IF(MONTH($A67) = 4, YEAR($A67)&amp;"-Q2", IF(MONTH($A67) = 7, YEAR($A67)&amp;"-Q3", IF(MONTH($A67) = 10, YEAR($A67)&amp;"-Q4",""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
         <v>38534</v>
       </c>
@@ -4072,15 +3592,8 @@
       <c r="O68">
         <v>-1.18360389148258E-2</v>
       </c>
-      <c r="P68">
-        <v>-11.3</v>
-      </c>
-      <c r="Q68" t="str">
-        <f t="shared" si="1"/>
-        <v>2005-Q3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
         <v>38565</v>
       </c>
@@ -4117,15 +3630,8 @@
       <c r="O69">
         <v>4.4601610835330902E-2</v>
       </c>
-      <c r="P69">
-        <v>-9.1999999999999993</v>
-      </c>
-      <c r="Q69" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
         <v>38596</v>
       </c>
@@ -4162,15 +3668,8 @@
       <c r="O70">
         <v>-3.6206104448727003E-2</v>
       </c>
-      <c r="P70">
-        <v>-7.2</v>
-      </c>
-      <c r="Q70" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
         <v>38626</v>
       </c>
@@ -4207,15 +3706,8 @@
       <c r="O71">
         <v>2.9091787743288602E-2</v>
       </c>
-      <c r="P71">
-        <v>-12.5</v>
-      </c>
-      <c r="Q71" t="str">
-        <f t="shared" si="1"/>
-        <v>2005-Q4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>38657</v>
       </c>
@@ -4252,15 +3744,8 @@
       <c r="O72">
         <v>3.1851352389182401E-2</v>
       </c>
-      <c r="P72">
-        <v>-13.9</v>
-      </c>
-      <c r="Q72" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>38687</v>
       </c>
@@ -4297,15 +3782,8 @@
       <c r="O73">
         <v>4.8183789635990203E-2</v>
       </c>
-      <c r="P73">
-        <v>-10.5</v>
-      </c>
-      <c r="Q73" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
         <v>38718</v>
       </c>
@@ -4342,15 +3820,8 @@
       <c r="O74">
         <v>1.0546466566003301E-2</v>
       </c>
-      <c r="P74">
-        <v>-9</v>
-      </c>
-      <c r="Q74" t="str">
-        <f t="shared" si="1"/>
-        <v>2006-Q1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
         <v>38749</v>
       </c>
@@ -4387,15 +3858,8 @@
       <c r="O75">
         <v>4.31322951490909E-2</v>
       </c>
-      <c r="P75">
-        <v>-9.6</v>
-      </c>
-      <c r="Q75" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
         <v>38777</v>
       </c>
@@ -4432,15 +3896,8 @@
       <c r="O76">
         <v>-6.2348969300725096E-3</v>
       </c>
-      <c r="P76">
-        <v>-10.8</v>
-      </c>
-      <c r="Q76" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
         <v>38808</v>
       </c>
@@ -4477,15 +3934,8 @@
       <c r="O77">
         <v>-5.10498114639528E-2</v>
       </c>
-      <c r="P77">
-        <v>-7.6</v>
-      </c>
-      <c r="Q77" t="str">
-        <f t="shared" si="1"/>
-        <v>2006-Q2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
         <v>38838</v>
       </c>
@@ -4522,15 +3972,8 @@
       <c r="O78">
         <v>7.2310902166368204E-3</v>
       </c>
-      <c r="P78">
-        <v>-12</v>
-      </c>
-      <c r="Q78" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
         <v>38869</v>
       </c>
@@ -4567,15 +4010,8 @@
       <c r="O79">
         <v>8.7134999213667203E-3</v>
       </c>
-      <c r="P79">
-        <v>-12.1</v>
-      </c>
-      <c r="Q79" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
         <v>38899</v>
       </c>
@@ -4612,15 +4048,8 @@
       <c r="O80">
         <v>3.05927302017714E-2</v>
       </c>
-      <c r="P80">
-        <v>-8.8000000000000007</v>
-      </c>
-      <c r="Q80" t="str">
-        <f t="shared" si="1"/>
-        <v>2006-Q3</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
         <v>38930</v>
       </c>
@@ -4657,15 +4086,8 @@
       <c r="O81">
         <v>1.63170821826828E-2</v>
       </c>
-      <c r="P81">
-        <v>-8.6999999999999993</v>
-      </c>
-      <c r="Q81" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
         <v>38961</v>
       </c>
@@ -4702,15 +4124,8 @@
       <c r="O82">
         <v>1.8629209178079999E-2</v>
       </c>
-      <c r="P82">
-        <v>-8.8000000000000007</v>
-      </c>
-      <c r="Q82" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
         <v>38991</v>
       </c>
@@ -4747,15 +4162,8 @@
       <c r="O83">
         <v>-3.9507568490417802E-3</v>
       </c>
-      <c r="P83">
-        <v>-6.7</v>
-      </c>
-      <c r="Q83" t="str">
-        <f t="shared" si="1"/>
-        <v>2006-Q4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
         <v>39022</v>
       </c>
@@ -4792,15 +4200,8 @@
       <c r="O84">
         <v>3.9403708494834398E-2</v>
       </c>
-      <c r="P84">
-        <v>-7.3</v>
-      </c>
-      <c r="Q84" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
         <v>39052</v>
       </c>
@@ -4837,15 +4238,8 @@
       <c r="O85">
         <v>1.1937339281487901E-2</v>
       </c>
-      <c r="P85">
-        <v>-7</v>
-      </c>
-      <c r="Q85" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
         <v>39083</v>
       </c>
@@ -4882,15 +4276,8 @@
       <c r="O86">
         <v>-1.6538497390584401E-2</v>
       </c>
-      <c r="P86">
-        <v>-6.8</v>
-      </c>
-      <c r="Q86" t="str">
-        <f t="shared" si="1"/>
-        <v>2007-Q1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
         <v>39114</v>
       </c>
@@ -4927,15 +4314,8 @@
       <c r="O87">
         <v>2.1137156353962201E-2</v>
       </c>
-      <c r="P87">
-        <v>-6.1</v>
-      </c>
-      <c r="Q87" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A88" s="4">
         <v>39142</v>
       </c>
@@ -4972,15 +4352,8 @@
       <c r="O88">
         <v>5.62291032286115E-2</v>
       </c>
-      <c r="P88">
-        <v>-6.3</v>
-      </c>
-      <c r="Q88" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A89" s="4">
         <v>39173</v>
       </c>
@@ -5017,15 +4390,8 @@
       <c r="O89">
         <v>2.38670949639559E-2</v>
       </c>
-      <c r="P89">
-        <v>-5.9</v>
-      </c>
-      <c r="Q89" t="str">
-        <f t="shared" si="1"/>
-        <v>2007-Q2</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
         <v>39203</v>
       </c>
@@ -5062,15 +4428,8 @@
       <c r="O90">
         <v>-8.0714487064721396E-3</v>
       </c>
-      <c r="P90">
-        <v>-1.7</v>
-      </c>
-      <c r="Q90" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A91" s="4">
         <v>39234</v>
       </c>
@@ -5107,15 +4466,8 @@
       <c r="O91">
         <v>-5.1485168432174398E-2</v>
       </c>
-      <c r="P91">
-        <v>-1.4</v>
-      </c>
-      <c r="Q91" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A92" s="4">
         <v>39264</v>
       </c>
@@ -5152,15 +4504,8 @@
       <c r="O92">
         <v>-1.5486832078741099E-2</v>
       </c>
-      <c r="P92">
-        <v>-2.4</v>
-      </c>
-      <c r="Q92" t="str">
-        <f t="shared" si="1"/>
-        <v>2007-Q3</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A93" s="4">
         <v>39295</v>
       </c>
@@ -5197,15 +4542,8 @@
       <c r="O93">
         <v>9.3141698508834008E-3</v>
       </c>
-      <c r="P93">
-        <v>-4.3</v>
-      </c>
-      <c r="Q93" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A94" s="4">
         <v>39326</v>
       </c>
@@ -5242,15 +4580,8 @@
       <c r="O94">
         <v>2.2876191262129801E-2</v>
       </c>
-      <c r="P94">
-        <v>-6.4</v>
-      </c>
-      <c r="Q94" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A95" s="4">
         <v>39356</v>
       </c>
@@ -5287,15 +4618,8 @@
       <c r="O95">
         <v>-3.0801595089171099E-2</v>
       </c>
-      <c r="P95">
-        <v>-7.1</v>
-      </c>
-      <c r="Q95" t="str">
-        <f t="shared" si="1"/>
-        <v>2007-Q4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A96" s="4">
         <v>39387</v>
       </c>
@@ -5332,15 +4656,8 @@
       <c r="O96">
         <v>-1.00118689454831E-2</v>
       </c>
-      <c r="P96">
-        <v>-11.2</v>
-      </c>
-      <c r="Q96" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A97" s="4">
         <v>39417</v>
       </c>
@@ -5377,15 +4694,8 @@
       <c r="O97">
         <v>-0.14222691880687699</v>
       </c>
-      <c r="P97">
-        <v>-9.9</v>
-      </c>
-      <c r="Q97" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A98" s="4">
         <v>39448</v>
       </c>
@@ -5422,15 +4732,8 @@
       <c r="O98">
         <v>-1.6382601433276599E-2</v>
       </c>
-      <c r="P98">
-        <v>-14.6</v>
-      </c>
-      <c r="Q98" t="str">
-        <f t="shared" si="1"/>
-        <v>2008-Q1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A99" s="4">
         <v>39479</v>
       </c>
@@ -5467,15 +4770,8 @@
       <c r="O99">
         <v>-1.7602625170612299E-2</v>
       </c>
-      <c r="P99">
-        <v>-13.6</v>
-      </c>
-      <c r="Q99" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A100" s="4">
         <v>39508</v>
       </c>
@@ -5512,15 +4808,8 @@
       <c r="O100">
         <v>5.9680084277132998E-2</v>
       </c>
-      <c r="P100">
-        <v>-14.5</v>
-      </c>
-      <c r="Q100" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
         <v>39539</v>
       </c>
@@ -5557,15 +4846,8 @@
       <c r="O101">
         <v>3.5441182588407099E-3</v>
       </c>
-      <c r="P101">
-        <v>-15.7</v>
-      </c>
-      <c r="Q101" t="str">
-        <f t="shared" si="1"/>
-        <v>2008-Q2</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A102" s="4">
         <v>39569</v>
       </c>
@@ -5602,15 +4884,8 @@
       <c r="O102">
         <v>-0.12279598363005</v>
       </c>
-      <c r="P102">
-        <v>-17.600000000000001</v>
-      </c>
-      <c r="Q102" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A103" s="4">
         <v>39600</v>
       </c>
@@ -5647,15 +4922,8 @@
       <c r="O103">
         <v>-9.6271784035604196E-3</v>
       </c>
-      <c r="P103">
-        <v>-20.6</v>
-      </c>
-      <c r="Q103" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A104" s="4">
         <v>39630</v>
       </c>
@@ -5692,15 +4960,8 @@
       <c r="O104">
         <v>2.03366200785755E-2</v>
       </c>
-      <c r="P104">
-        <v>-19.899999999999999</v>
-      </c>
-      <c r="Q104" t="str">
-        <f t="shared" si="1"/>
-        <v>2008-Q3</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A105" s="4">
         <v>39661</v>
       </c>
@@ -5737,15 +4998,8 @@
       <c r="O105">
         <v>-0.105915900744787</v>
       </c>
-      <c r="P105">
-        <v>-18.3</v>
-      </c>
-      <c r="Q105" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A106" s="4">
         <v>39692</v>
       </c>
@@ -5782,15 +5036,8 @@
       <c r="O106">
         <v>-0.14522549461015699</v>
       </c>
-      <c r="P106">
-        <v>-17.2</v>
-      </c>
-      <c r="Q106" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A107" s="4">
         <v>39722</v>
       </c>
@@ -5827,15 +5074,8 @@
       <c r="O107">
         <v>-6.6512939069601998E-2</v>
       </c>
-      <c r="P107">
-        <v>-19.8</v>
-      </c>
-      <c r="Q107" t="str">
-        <f t="shared" si="1"/>
-        <v>2008-Q4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A108" s="4">
         <v>39753</v>
       </c>
@@ -5872,15 +5112,8 @@
       <c r="O108">
         <v>-1.3798205726763201E-2</v>
       </c>
-      <c r="P108">
-        <v>-16.899999999999999</v>
-      </c>
-      <c r="Q108" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A109" s="4">
         <v>39783</v>
       </c>
@@ -5917,15 +5150,8 @@
       <c r="O109">
         <v>-7.8869795254126601E-2</v>
       </c>
-      <c r="P109">
-        <v>-18.3</v>
-      </c>
-      <c r="Q109" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A110" s="4">
         <v>39814</v>
       </c>
@@ -5962,15 +5188,8 @@
       <c r="O110">
         <v>-9.5711058886221806E-2</v>
       </c>
-      <c r="P110">
-        <v>-18</v>
-      </c>
-      <c r="Q110" t="str">
-        <f t="shared" si="1"/>
-        <v>2009-Q1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A111" s="4">
         <v>39845</v>
       </c>
@@ -6007,15 +5226,8 @@
       <c r="O111">
         <v>3.8067584387445001E-2</v>
       </c>
-      <c r="P111">
-        <v>-19</v>
-      </c>
-      <c r="Q111" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
         <v>39873</v>
       </c>
@@ -6052,15 +5264,8 @@
       <c r="O112">
         <v>0.11828714191398899</v>
       </c>
-      <c r="P112">
-        <v>-19.899999999999999</v>
-      </c>
-      <c r="Q112" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A113" s="4">
         <v>39904</v>
       </c>
@@ -6097,15 +5302,8 @@
       <c r="O113">
         <v>3.6602083381177798E-2</v>
       </c>
-      <c r="P113">
-        <v>-15.7</v>
-      </c>
-      <c r="Q113" t="str">
-        <f t="shared" si="1"/>
-        <v>2009-Q2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A114" s="4">
         <v>39934</v>
       </c>
@@ -6142,15 +5340,8 @@
       <c r="O114">
         <v>-4.2763773570298397E-2</v>
       </c>
-      <c r="P114">
-        <v>-15.4</v>
-      </c>
-      <c r="Q114" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A115" s="4">
         <v>39965</v>
       </c>
@@ -6187,15 +5378,8 @@
       <c r="O115">
         <v>8.7109312769969804E-2</v>
       </c>
-      <c r="P115">
-        <v>-14</v>
-      </c>
-      <c r="Q115" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A116" s="4">
         <v>39995</v>
       </c>
@@ -6232,15 +5416,8 @@
       <c r="O116">
         <v>6.4224359682599499E-2</v>
       </c>
-      <c r="P116">
-        <v>-13.4</v>
-      </c>
-      <c r="Q116" t="str">
-        <f t="shared" si="1"/>
-        <v>2009-Q3</v>
-      </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A117" s="4">
         <v>40026</v>
       </c>
@@ -6277,15 +5454,8 @@
       <c r="O117">
         <v>3.8095847459066703E-2</v>
       </c>
-      <c r="P117">
-        <v>-15.8</v>
-      </c>
-      <c r="Q117" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A118" s="4">
         <v>40057</v>
       </c>
@@ -6322,15 +5492,8 @@
       <c r="O118">
         <v>-5.0724756655295501E-2</v>
       </c>
-      <c r="P118">
-        <v>-11.6</v>
-      </c>
-      <c r="Q118" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A119" s="4">
         <v>40087</v>
       </c>
@@ -6367,15 +5530,8 @@
       <c r="O119">
         <v>1.9885823593464001E-2</v>
       </c>
-      <c r="P119">
-        <v>-10.4</v>
-      </c>
-      <c r="Q119" t="str">
-        <f t="shared" si="1"/>
-        <v>2009-Q4</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A120" s="4">
         <v>40118</v>
       </c>
@@ -6412,15 +5568,8 @@
       <c r="O120">
         <v>6.7295351302329096E-2</v>
       </c>
-      <c r="P120">
-        <v>-8.5</v>
-      </c>
-      <c r="Q120" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A121" s="4">
         <v>40148</v>
       </c>
@@ -6457,15 +5606,8 @@
       <c r="O121">
         <v>-5.1307631456934302E-2</v>
       </c>
-      <c r="P121">
-        <v>-9</v>
-      </c>
-      <c r="Q121" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A122" s="4">
         <v>40179</v>
       </c>
@@ -6502,15 +5644,8 @@
       <c r="O122">
         <v>-8.2328182003816898E-3</v>
       </c>
-      <c r="P122">
-        <v>-8.1999999999999993</v>
-      </c>
-      <c r="Q122" t="str">
-        <f t="shared" si="1"/>
-        <v>2010-Q1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
         <v>40210</v>
       </c>
@@ -6547,15 +5682,8 @@
       <c r="O123">
         <v>6.9067275611374199E-2</v>
       </c>
-      <c r="P123">
-        <v>-10.6</v>
-      </c>
-      <c r="Q123" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A124" s="4">
         <v>40238</v>
       </c>
@@ -6592,15 +5720,8 @@
       <c r="O124">
         <v>-4.0313511597476599E-2</v>
       </c>
-      <c r="P124">
-        <v>-12.5</v>
-      </c>
-      <c r="Q124" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A125" s="4">
         <v>40269</v>
       </c>
@@ -6637,15 +5758,8 @@
       <c r="O125">
         <v>-8.4541495588513996E-2</v>
       </c>
-      <c r="P125">
-        <v>-12.4</v>
-      </c>
-      <c r="Q125" t="str">
-        <f t="shared" si="1"/>
-        <v>2010-Q2</v>
-      </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A126" s="4">
         <v>40299</v>
       </c>
@@ -6682,15 +5796,8 @@
       <c r="O126">
         <v>-1.8609451991013201E-2</v>
       </c>
-      <c r="P126">
-        <v>-14.8</v>
-      </c>
-      <c r="Q126" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A127" s="4">
         <v>40330</v>
       </c>
@@ -6727,15 +5834,8 @@
       <c r="O127">
         <v>5.6534713904302002E-2</v>
       </c>
-      <c r="P127">
-        <v>-15.6</v>
-      </c>
-      <c r="Q127" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A128" s="4">
         <v>40360</v>
       </c>
@@ -6772,15 +5872,8 @@
       <c r="O128">
         <v>-4.2717834847223898E-2</v>
       </c>
-      <c r="P128">
-        <v>-14.8</v>
-      </c>
-      <c r="Q128" t="str">
-        <f t="shared" si="1"/>
-        <v>2010-Q3</v>
-      </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A129" s="4">
         <v>40391</v>
       </c>
@@ -6817,15 +5910,8 @@
       <c r="O129">
         <v>6.2299027996440201E-2</v>
       </c>
-      <c r="P129">
-        <v>-12.9</v>
-      </c>
-      <c r="Q129" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A130" s="4">
         <v>40422</v>
       </c>
@@ -6862,15 +5948,8 @@
       <c r="O130">
         <v>3.13511132001505E-2</v>
       </c>
-      <c r="P130">
-        <v>-13.7</v>
-      </c>
-      <c r="Q130" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A131" s="4">
         <v>40452</v>
       </c>
@@ -6907,15 +5986,8 @@
       <c r="O131">
         <v>-5.9948591671700399E-2</v>
       </c>
-      <c r="P131">
-        <v>-12.5</v>
-      </c>
-      <c r="Q131" t="str">
-        <f t="shared" ref="Q131:Q194" si="2">IF(MONTH($A131) = 1, YEAR($A131)&amp;"-Q"&amp;MONTH($A131), IF(MONTH($A131) = 4, YEAR($A131)&amp;"-Q2", IF(MONTH($A131) = 7, YEAR($A131)&amp;"-Q3", IF(MONTH($A131) = 10, YEAR($A131)&amp;"-Q4",""))))</f>
-        <v>2010-Q4</v>
-      </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A132" s="4">
         <v>40483</v>
       </c>
@@ -6952,15 +6024,8 @@
       <c r="O132">
         <v>5.2428546337333501E-2</v>
       </c>
-      <c r="P132">
-        <v>-9.4</v>
-      </c>
-      <c r="Q132" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A133" s="4">
         <v>40513</v>
       </c>
@@ -6997,15 +6062,8 @@
       <c r="O133">
         <v>5.1410237990589601E-2</v>
       </c>
-      <c r="P133">
-        <v>-12.4</v>
-      </c>
-      <c r="Q133" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
         <v>40544</v>
       </c>
@@ -7042,15 +6100,8 @@
       <c r="O134">
         <v>2.5839790118832098E-2</v>
       </c>
-      <c r="P134">
-        <v>-14.4</v>
-      </c>
-      <c r="Q134" t="str">
-        <f t="shared" si="2"/>
-        <v>2011-Q1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A135" s="4">
         <v>40575</v>
       </c>
@@ -7087,15 +6138,8 @@
       <c r="O135">
         <v>-2.9922527931605099E-2</v>
       </c>
-      <c r="P135">
-        <v>-14.8</v>
-      </c>
-      <c r="Q135" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A136" s="4">
         <v>40603</v>
       </c>
@@ -7132,15 +6176,8 @@
       <c r="O136">
         <v>2.90876579632737E-2</v>
       </c>
-      <c r="P136">
-        <v>-16</v>
-      </c>
-      <c r="Q136" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A137" s="4">
         <v>40634</v>
       </c>
@@ -7177,15 +6214,8 @@
       <c r="O137">
         <v>-2.4645493700560898E-2</v>
       </c>
-      <c r="P137">
-        <v>-16.600000000000001</v>
-      </c>
-      <c r="Q137" t="str">
-        <f t="shared" si="2"/>
-        <v>2011-Q2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A138" s="4">
         <v>40664</v>
       </c>
@@ -7222,15 +6252,8 @@
       <c r="O138">
         <v>-6.1909113628555402E-3</v>
       </c>
-      <c r="P138">
-        <v>-15.4</v>
-      </c>
-      <c r="Q138" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A139" s="4">
         <v>40695</v>
       </c>
@@ -7267,15 +6290,8 @@
       <c r="O139">
         <v>-8.0890780677837198E-2</v>
       </c>
-      <c r="P139">
-        <v>-16.100000000000001</v>
-      </c>
-      <c r="Q139" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A140" s="4">
         <v>40725</v>
       </c>
@@ -7312,15 +6328,8 @@
       <c r="O140">
         <v>-0.120213311947099</v>
       </c>
-      <c r="P140">
-        <v>-15</v>
-      </c>
-      <c r="Q140" t="str">
-        <f t="shared" si="2"/>
-        <v>2011-Q3</v>
-      </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A141" s="4">
         <v>40756</v>
       </c>
@@ -7357,15 +6366,8 @@
       <c r="O141">
         <v>-8.8152049798438298E-2</v>
       </c>
-      <c r="P141">
-        <v>-19</v>
-      </c>
-      <c r="Q141" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A142" s="4">
         <v>40787</v>
       </c>
@@ -7402,15 +6404,8 @@
       <c r="O142">
         <v>8.38687268406932E-2</v>
       </c>
-      <c r="P142">
-        <v>-18.7</v>
-      </c>
-      <c r="Q142" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A143" s="4">
         <v>40817</v>
       </c>
@@ -7447,15 +6442,8 @@
       <c r="O143">
         <v>-2.7581434030389901E-2</v>
       </c>
-      <c r="P143">
-        <v>-16.2</v>
-      </c>
-      <c r="Q143" t="str">
-        <f t="shared" si="2"/>
-        <v>2011-Q4</v>
-      </c>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A144" s="4">
         <v>40848</v>
       </c>
@@ -7492,15 +6480,8 @@
       <c r="O144">
         <v>1.64383560525927E-3</v>
       </c>
-      <c r="P144">
-        <v>-18.899999999999999</v>
-      </c>
-      <c r="Q144" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
         <v>40878</v>
       </c>
@@ -7537,15 +6518,8 @@
       <c r="O145">
         <v>4.2971075021835503E-2</v>
       </c>
-      <c r="P145">
-        <v>-19.8</v>
-      </c>
-      <c r="Q145" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A146" s="4">
         <v>40909</v>
       </c>
@@ -7582,15 +6556,8 @@
       <c r="O146">
         <v>4.5601117020028802E-2</v>
       </c>
-      <c r="P146">
-        <v>-18.8</v>
-      </c>
-      <c r="Q146" t="str">
-        <f t="shared" si="2"/>
-        <v>2012-Q1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A147" s="4">
         <v>40940</v>
       </c>
@@ -7627,15 +6594,8 @@
       <c r="O147">
         <v>-8.3301265949344803E-3</v>
       </c>
-      <c r="P147">
-        <v>-16.8</v>
-      </c>
-      <c r="Q147" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A148" s="4">
         <v>40969</v>
       </c>
@@ -7672,15 +6632,8 @@
       <c r="O148">
         <v>-6.3611136926022396E-2</v>
       </c>
-      <c r="P148">
-        <v>-13.3</v>
-      </c>
-      <c r="Q148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A149" s="4">
         <v>41000</v>
       </c>
@@ -7717,15 +6670,8 @@
       <c r="O149">
         <v>-6.2876568314051098E-2</v>
       </c>
-      <c r="P149">
-        <v>-13.6</v>
-      </c>
-      <c r="Q149" t="str">
-        <f t="shared" si="2"/>
-        <v>2012-Q2</v>
-      </c>
-    </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A150" s="4">
         <v>41030</v>
       </c>
@@ -7762,15 +6708,8 @@
       <c r="O150">
         <v>5.7837077940583001E-2</v>
       </c>
-      <c r="P150">
-        <v>-11.3</v>
-      </c>
-      <c r="Q150" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A151" s="4">
         <v>41061</v>
       </c>
@@ -7807,15 +6746,8 @@
       <c r="O151">
         <v>2.92886141998192E-2</v>
       </c>
-      <c r="P151">
-        <v>-12.2</v>
-      </c>
-      <c r="Q151" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A152" s="4">
         <v>41091</v>
       </c>
@@ -7852,15 +6784,8 @@
       <c r="O152">
         <v>3.6220229458797E-2</v>
       </c>
-      <c r="P152">
-        <v>-15.7</v>
-      </c>
-      <c r="Q152" t="str">
-        <f t="shared" si="2"/>
-        <v>2012-Q3</v>
-      </c>
-    </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A153" s="4">
         <v>41122</v>
       </c>
@@ -7897,15 +6822,8 @@
       <c r="O153">
         <v>-1.7214061464299501E-2</v>
       </c>
-      <c r="P153">
-        <v>-16</v>
-      </c>
-      <c r="Q153" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A154" s="4">
         <v>41153</v>
       </c>
@@ -7942,15 +6860,8 @@
       <c r="O154">
         <v>2.1949278139810999E-2</v>
       </c>
-      <c r="P154">
-        <v>-18.899999999999999</v>
-      </c>
-      <c r="Q154" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A155" s="4">
         <v>41183</v>
       </c>
@@ -7987,15 +6898,8 @@
       <c r="O155">
         <v>3.6648799890897997E-2</v>
       </c>
-      <c r="P155">
-        <v>-19.3</v>
-      </c>
-      <c r="Q155" t="str">
-        <f t="shared" si="2"/>
-        <v>2012-Q4</v>
-      </c>
-    </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
         <v>41214</v>
       </c>
@@ -8032,15 +6936,8 @@
       <c r="O156">
         <v>2.3281397145748201E-2</v>
       </c>
-      <c r="P156">
-        <v>-18.3</v>
-      </c>
-      <c r="Q156" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A157" s="4">
         <v>41244</v>
       </c>
@@ -8077,15 +6974,8 @@
       <c r="O157">
         <v>2.4827454659433802E-2</v>
       </c>
-      <c r="P157">
-        <v>-18</v>
-      </c>
-      <c r="Q157" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A158" s="4">
         <v>41275</v>
       </c>
@@ -8122,15 +7012,8 @@
       <c r="O158">
         <v>-2.5752730393744398E-3</v>
       </c>
-      <c r="P158">
-        <v>-19.2</v>
-      </c>
-      <c r="Q158" t="str">
-        <f t="shared" si="2"/>
-        <v>2013-Q1</v>
-      </c>
-    </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A159" s="4">
         <v>41306</v>
       </c>
@@ -8167,15 +7050,8 @@
       <c r="O159">
         <v>2.25904243227681E-3</v>
       </c>
-      <c r="P159">
-        <v>-18.8</v>
-      </c>
-      <c r="Q159" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A160" s="4">
         <v>41334</v>
       </c>
@@ -8212,15 +7088,8 @@
       <c r="O160">
         <v>3.3036022587055E-2</v>
       </c>
-      <c r="P160">
-        <v>-19.899999999999999</v>
-      </c>
-      <c r="Q160" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A161" s="4">
         <v>41365</v>
       </c>
@@ -8257,15 +7126,8 @@
       <c r="O161">
         <v>2.3533715510430001E-2</v>
       </c>
-      <c r="P161">
-        <v>-19.399999999999999</v>
-      </c>
-      <c r="Q161" t="str">
-        <f t="shared" si="2"/>
-        <v>2013-Q2</v>
-      </c>
-    </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A162" s="4">
         <v>41395</v>
       </c>
@@ -8302,15 +7164,8 @@
       <c r="O162">
         <v>-5.4564473829199003E-2</v>
       </c>
-      <c r="P162">
-        <v>-22.1</v>
-      </c>
-      <c r="Q162" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A163" s="4">
         <v>41426</v>
       </c>
@@ -8347,15 +7202,8 @@
       <c r="O163">
         <v>6.5671072938105396E-2</v>
       </c>
-      <c r="P163">
-        <v>-22</v>
-      </c>
-      <c r="Q163" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A164" s="4">
         <v>41456</v>
       </c>
@@ -8392,15 +7240,8 @@
       <c r="O164">
         <v>-1.4864371403565E-2</v>
       </c>
-      <c r="P164">
-        <v>-19.3</v>
-      </c>
-      <c r="Q164" t="str">
-        <f t="shared" si="2"/>
-        <v>2013-Q3</v>
-      </c>
-    </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A165" s="4">
         <v>41487</v>
       </c>
@@ -8437,15 +7278,8 @@
       <c r="O165">
         <v>5.19255434234598E-2</v>
       </c>
-      <c r="P165">
-        <v>-16.399999999999999</v>
-      </c>
-      <c r="Q165" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A166" s="4">
         <v>41518</v>
       </c>
@@ -8482,15 +7316,8 @@
       <c r="O166">
         <v>3.70631262236856E-2</v>
       </c>
-      <c r="P166">
-        <v>-15.1</v>
-      </c>
-      <c r="Q166" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
         <v>41548</v>
       </c>
@@ -8527,15 +7354,8 @@
       <c r="O167">
         <v>-1.08903356345458E-3</v>
       </c>
-      <c r="P167">
-        <v>-14.8</v>
-      </c>
-      <c r="Q167" t="str">
-        <f t="shared" si="2"/>
-        <v>2013-Q4</v>
-      </c>
-    </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A168" s="4">
         <v>41579</v>
       </c>
@@ -8572,15 +7392,8 @@
       <c r="O168">
         <v>1.72324660084655E-4</v>
       </c>
-      <c r="P168">
-        <v>-18.100000000000001</v>
-      </c>
-      <c r="Q168" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A169" s="4">
         <v>41609</v>
       </c>
@@ -8617,15 +7430,8 @@
       <c r="O169">
         <v>-3.0783582468925999E-2</v>
       </c>
-      <c r="P169">
-        <v>-16.600000000000001</v>
-      </c>
-      <c r="Q169" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A170" s="4">
         <v>41640</v>
       </c>
@@ -8662,15 +7468,8 @@
       <c r="O170">
         <v>5.6550056828855902E-2</v>
       </c>
-      <c r="P170">
-        <v>-16</v>
-      </c>
-      <c r="Q170" t="str">
-        <f t="shared" si="2"/>
-        <v>2014-Q1</v>
-      </c>
-    </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A171" s="4">
         <v>41671</v>
       </c>
@@ -8707,15 +7506,8 @@
       <c r="O171">
         <v>-3.7683838543536301E-3</v>
       </c>
-      <c r="P171">
-        <v>-16.100000000000001</v>
-      </c>
-      <c r="Q171" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A172" s="4">
         <v>41699</v>
       </c>
@@ -8752,15 +7544,8 @@
       <c r="O172">
         <v>2.1600417071425699E-2</v>
       </c>
-      <c r="P172">
-        <v>-15.2</v>
-      </c>
-      <c r="Q172" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A173" s="4">
         <v>41730</v>
       </c>
@@ -8797,15 +7582,8 @@
       <c r="O173">
         <v>7.1455462355522999E-3</v>
       </c>
-      <c r="P173">
-        <v>-16.2</v>
-      </c>
-      <c r="Q173" t="str">
-        <f t="shared" si="2"/>
-        <v>2014-Q2</v>
-      </c>
-    </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A174" s="4">
         <v>41760</v>
       </c>
@@ -8842,15 +7620,8 @@
       <c r="O174">
         <v>-2.16348293202842E-2</v>
       </c>
-      <c r="P174">
-        <v>-16.8</v>
-      </c>
-      <c r="Q174" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A175" s="4">
         <v>41791</v>
       </c>
@@ -8887,15 +7658,8 @@
       <c r="O175">
         <v>-4.0771621216736199E-2</v>
       </c>
-      <c r="P175">
-        <v>-18</v>
-      </c>
-      <c r="Q175" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A176" s="4">
         <v>41821</v>
       </c>
@@ -8932,15 +7696,8 @@
       <c r="O176">
         <v>3.1275780896889302E-2</v>
       </c>
-      <c r="P176">
-        <v>-16.399999999999999</v>
-      </c>
-      <c r="Q176" t="str">
-        <f t="shared" si="2"/>
-        <v>2014-Q3</v>
-      </c>
-    </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A177" s="4">
         <v>41852</v>
       </c>
@@ -8977,15 +7734,8 @@
       <c r="O177">
         <v>8.0025603533719902E-3</v>
       </c>
-      <c r="P177">
-        <v>-16.5</v>
-      </c>
-      <c r="Q177" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
         <v>41883</v>
       </c>
@@ -9022,15 +7772,8 @@
       <c r="O178">
         <v>-4.2356522477407003E-2</v>
       </c>
-      <c r="P178">
-        <v>-17.600000000000001</v>
-      </c>
-      <c r="Q178" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A179" s="4">
         <v>41913</v>
       </c>
@@ -9067,15 +7810,8 @@
       <c r="O179">
         <v>3.6438082646212101E-2</v>
       </c>
-      <c r="P179">
-        <v>-17</v>
-      </c>
-      <c r="Q179" t="str">
-        <f t="shared" si="2"/>
-        <v>2014-Q4</v>
-      </c>
-    </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A180" s="4">
         <v>41944</v>
       </c>
@@ -9112,15 +7848,8 @@
       <c r="O180">
         <v>-2.71126205175811E-2</v>
       </c>
-      <c r="P180">
-        <v>-16.2</v>
-      </c>
-      <c r="Q180" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A181" s="4">
         <v>41974</v>
       </c>
@@ -9157,15 +7886,8 @@
       <c r="O181">
         <v>7.4722141947100695E-2</v>
       </c>
-      <c r="P181">
-        <v>-14.2</v>
-      </c>
-      <c r="Q181" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A182" s="4">
         <v>42005</v>
       </c>
@@ -9202,15 +7924,8 @@
       <c r="O182">
         <v>7.2706727852910505E-2</v>
       </c>
-      <c r="P182">
-        <v>-13.6</v>
-      </c>
-      <c r="Q182" t="str">
-        <f t="shared" si="2"/>
-        <v>2015-Q1</v>
-      </c>
-    </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A183" s="4">
         <v>42036</v>
       </c>
@@ -9247,15 +7962,8 @@
       <c r="O183">
         <v>1.6456889763624399E-2</v>
       </c>
-      <c r="P183">
-        <v>-11.2</v>
-      </c>
-      <c r="Q183" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A184" s="4">
         <v>42064</v>
       </c>
@@ -9292,15 +8000,8 @@
       <c r="O184">
         <v>2.54959095648388E-3</v>
       </c>
-      <c r="P184">
-        <v>-10.7</v>
-      </c>
-      <c r="Q184" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A185" s="4">
         <v>42095</v>
       </c>
@@ -9337,15 +8038,8 @@
       <c r="O185">
         <v>-7.6783025655924302E-3</v>
       </c>
-      <c r="P185">
-        <v>-10.1</v>
-      </c>
-      <c r="Q185" t="str">
-        <f t="shared" si="2"/>
-        <v>2015-Q2</v>
-      </c>
-    </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A186" s="4">
         <v>42125</v>
       </c>
@@ -9382,15 +8076,8 @@
       <c r="O186">
         <v>-4.4442491023046302E-2</v>
       </c>
-      <c r="P186">
-        <v>-12</v>
-      </c>
-      <c r="Q186" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A187" s="4">
         <v>42156</v>
       </c>
@@ -9427,15 +8114,8 @@
       <c r="O187">
         <v>5.9252677301159899E-2</v>
       </c>
-      <c r="P187">
-        <v>-11.8</v>
-      </c>
-      <c r="Q187" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A188" s="4">
         <v>42186</v>
       </c>
@@ -9472,15 +8152,8 @@
       <c r="O188">
         <v>-8.8323413253712998E-2</v>
       </c>
-      <c r="P188">
-        <v>-12.9</v>
-      </c>
-      <c r="Q188" t="str">
-        <f t="shared" si="2"/>
-        <v>2015-Q3</v>
-      </c>
-    </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
         <v>42217</v>
       </c>
@@ -9517,15 +8190,8 @@
       <c r="O189">
         <v>-4.3409306055151503E-2</v>
       </c>
-      <c r="P189">
-        <v>-11.1</v>
-      </c>
-      <c r="Q189" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A190" s="4">
         <v>42248</v>
       </c>
@@ -9562,15 +8228,8 @@
       <c r="O190">
         <v>9.4665408965104406E-2</v>
       </c>
-      <c r="P190">
-        <v>-10.199999999999999</v>
-      </c>
-      <c r="Q190" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A191" s="4">
         <v>42278</v>
       </c>
@@ -9607,15 +8266,8 @@
       <c r="O191">
         <v>1.2164200428692601E-2</v>
       </c>
-      <c r="P191">
-        <v>-9.9</v>
-      </c>
-      <c r="Q191" t="str">
-        <f t="shared" si="2"/>
-        <v>2015-Q4</v>
-      </c>
-    </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A192" s="4">
         <v>42309</v>
       </c>
@@ -9652,15 +8304,8 @@
       <c r="O192">
         <v>-6.6841215001996801E-2</v>
       </c>
-      <c r="P192">
-        <v>-9.1</v>
-      </c>
-      <c r="Q192" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A193" s="4">
         <v>42339</v>
       </c>
@@ -9697,15 +8342,8 @@
       <c r="O193">
         <v>-4.8615292375945501E-2</v>
       </c>
-      <c r="P193">
-        <v>-9.5</v>
-      </c>
-      <c r="Q193" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A194" s="4">
         <v>42370</v>
       </c>
@@ -9742,15 +8380,8 @@
       <c r="O194">
         <v>-1.4473705616282501E-2</v>
       </c>
-      <c r="P194">
-        <v>-8.3000000000000007</v>
-      </c>
-      <c r="Q194" t="str">
-        <f t="shared" si="2"/>
-        <v>2016-Q1</v>
-      </c>
-    </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A195" s="4">
         <v>42401</v>
       </c>
@@ -9787,15 +8418,8 @@
       <c r="O195">
         <v>7.2117627331031997E-3</v>
       </c>
-      <c r="P195">
-        <v>-10.6</v>
-      </c>
-      <c r="Q195" t="str">
-        <f t="shared" ref="Q195:Q258" si="3">IF(MONTH($A195) = 1, YEAR($A195)&amp;"-Q"&amp;MONTH($A195), IF(MONTH($A195) = 4, YEAR($A195)&amp;"-Q2", IF(MONTH($A195) = 7, YEAR($A195)&amp;"-Q3", IF(MONTH($A195) = 10, YEAR($A195)&amp;"-Q4",""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A196" s="4">
         <v>42430</v>
       </c>
@@ -9832,15 +8456,8 @@
       <c r="O196">
         <v>9.9614625934982808E-3</v>
       </c>
-      <c r="P196">
-        <v>-12</v>
-      </c>
-      <c r="Q196" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A197" s="4">
         <v>42461</v>
       </c>
@@ -9877,15 +8494,8 @@
       <c r="O197">
         <v>1.7160747764890499E-2</v>
       </c>
-      <c r="P197">
-        <v>-11.9</v>
-      </c>
-      <c r="Q197" t="str">
-        <f t="shared" si="3"/>
-        <v>2016-Q2</v>
-      </c>
-    </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A198" s="4">
         <v>42491</v>
       </c>
@@ -9922,15 +8532,8 @@
       <c r="O198">
         <v>-6.1356784139066499E-2</v>
       </c>
-      <c r="P198">
-        <v>-9.5</v>
-      </c>
-      <c r="Q198" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A199" s="4">
         <v>42522</v>
       </c>
@@ -9967,15 +8570,8 @@
       <c r="O199">
         <v>4.6642847610806698E-2</v>
       </c>
-      <c r="P199">
-        <v>-12.1</v>
-      </c>
-      <c r="Q199" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
         <v>42552</v>
       </c>
@@ -10012,15 +8608,8 @@
       <c r="O200">
         <v>-3.5815236443958998E-4</v>
       </c>
-      <c r="P200">
-        <v>-11.7</v>
-      </c>
-      <c r="Q200" t="str">
-        <f t="shared" si="3"/>
-        <v>2016-Q3</v>
-      </c>
-    </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A201" s="4">
         <v>42583</v>
       </c>
@@ -10057,15 +8646,8 @@
       <c r="O201">
         <v>2.25951221960585E-3</v>
       </c>
-      <c r="P201">
-        <v>-11.1</v>
-      </c>
-      <c r="Q201" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A202" s="4">
         <v>42614</v>
       </c>
@@ -10102,15 +8684,8 @@
       <c r="O202">
         <v>1.3620052464799999E-2</v>
       </c>
-      <c r="P202">
-        <v>-9.6</v>
-      </c>
-      <c r="Q202" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A203" s="4">
         <v>42644</v>
       </c>
@@ -10147,15 +8722,8 @@
       <c r="O203">
         <v>1.52034446309166E-2</v>
       </c>
-      <c r="P203">
-        <v>-9.3000000000000007</v>
-      </c>
-      <c r="Q203" t="str">
-        <f t="shared" si="3"/>
-        <v>2016-Q4</v>
-      </c>
-    </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A204" s="4">
         <v>42675</v>
       </c>
@@ -10192,15 +8760,8 @@
       <c r="O204">
         <v>6.0177192797663502E-2</v>
       </c>
-      <c r="P204">
-        <v>-7.9</v>
-      </c>
-      <c r="Q204" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A205" s="4">
         <v>42705</v>
       </c>
@@ -10237,15 +8798,8 @@
       <c r="O205">
         <v>-2.3600653964940901E-2</v>
       </c>
-      <c r="P205">
-        <v>-6.9</v>
-      </c>
-      <c r="Q205" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A206" s="4">
         <v>42736</v>
       </c>
@@ -10282,15 +8836,8 @@
       <c r="O206">
         <v>2.28332385123746E-2</v>
       </c>
-      <c r="P206">
-        <v>-7.4</v>
-      </c>
-      <c r="Q206" t="str">
-        <f t="shared" si="3"/>
-        <v>2017-Q1</v>
-      </c>
-    </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A207" s="4">
         <v>42767</v>
       </c>
@@ -10327,15 +8874,8 @@
       <c r="O207">
         <v>5.2898277317826398E-2</v>
       </c>
-      <c r="P207">
-        <v>-8.1</v>
-      </c>
-      <c r="Q207" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A208" s="4">
         <v>42795</v>
       </c>
@@ -10372,15 +8912,8 @@
       <c r="O208">
         <v>2.78791000860714E-2</v>
       </c>
-      <c r="P208">
-        <v>-8.3000000000000007</v>
-      </c>
-      <c r="Q208" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A209" s="4">
         <v>42826</v>
       </c>
@@ -10417,15 +8950,8 @@
       <c r="O209">
         <v>3.0897316860159E-3</v>
       </c>
-      <c r="P209">
-        <v>-7.4</v>
-      </c>
-      <c r="Q209" t="str">
-        <f t="shared" si="3"/>
-        <v>2017-Q2</v>
-      </c>
-    </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A210" s="4">
         <v>42856</v>
       </c>
@@ -10462,15 +8988,8 @@
       <c r="O210">
         <v>-3.13260622586196E-2</v>
       </c>
-      <c r="P210">
-        <v>-6.7</v>
-      </c>
-      <c r="Q210" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
         <v>42887</v>
       </c>
@@ -10507,15 +9026,8 @@
       <c r="O211">
         <v>-5.2690488462960898E-3</v>
       </c>
-      <c r="P211">
-        <v>-2</v>
-      </c>
-      <c r="Q211" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A212" s="4">
         <v>42917</v>
       </c>
@@ -10552,15 +9064,8 @@
       <c r="O212">
         <v>-1.6072086362957101E-3</v>
       </c>
-      <c r="P212">
-        <v>-4.2</v>
-      </c>
-      <c r="Q212" t="str">
-        <f t="shared" si="3"/>
-        <v>2017-Q3</v>
-      </c>
-    </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A213" s="4">
         <v>42948</v>
       </c>
@@ -10597,15 +9102,8 @@
       <c r="O213">
         <v>4.6904581678674603E-2</v>
       </c>
-      <c r="P213">
-        <v>-5.8</v>
-      </c>
-      <c r="Q213" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A214" s="4">
         <v>42979</v>
       </c>
@@ -10642,15 +9140,8 @@
       <c r="O214">
         <v>3.2030501058789802E-2</v>
       </c>
-      <c r="P214">
-        <v>-7.2</v>
-      </c>
-      <c r="Q214" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A215" s="4">
         <v>43009</v>
       </c>
@@ -10687,15 +9178,8 @@
       <c r="O215">
         <v>-2.39987683723424E-2</v>
       </c>
-      <c r="P215">
-        <v>-7.3</v>
-      </c>
-      <c r="Q215" t="str">
-        <f t="shared" si="3"/>
-        <v>2017-Q4</v>
-      </c>
-    </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A216" s="4">
         <v>43040</v>
       </c>
@@ -10732,15 +9216,8 @@
       <c r="O216">
         <v>-1.12734946091724E-2</v>
       </c>
-      <c r="P216">
-        <v>-4.2</v>
-      </c>
-      <c r="Q216" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A217" s="4">
         <v>43070</v>
       </c>
@@ -10777,15 +9254,8 @@
       <c r="O217">
         <v>3.1383421468568401E-2</v>
       </c>
-      <c r="P217">
-        <v>-3.1</v>
-      </c>
-      <c r="Q217" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A218" s="4">
         <v>43101</v>
       </c>
@@ -10822,15 +9292,8 @@
       <c r="O218">
         <v>-2.9891812375584699E-2</v>
       </c>
-      <c r="P218">
-        <v>-4.0999999999999996</v>
-      </c>
-      <c r="Q218" t="str">
-        <f t="shared" si="3"/>
-        <v>2018-Q1</v>
-      </c>
-    </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A219" s="4">
         <v>43132</v>
       </c>
@@ -10867,15 +9330,8 @@
       <c r="O219">
         <v>-2.9215177834602798E-2</v>
       </c>
-      <c r="P219">
-        <v>-7</v>
-      </c>
-      <c r="Q219" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A220" s="4">
         <v>43160</v>
       </c>
@@ -10912,15 +9368,8 @@
       <c r="O220">
         <v>6.6118165304983406E-2</v>
       </c>
-      <c r="P220">
-        <v>-6.9</v>
-      </c>
-      <c r="Q220" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A221" s="4">
         <v>43191</v>
       </c>
@@ -10957,15 +9406,8 @@
       <c r="O221">
         <v>-2.23658406173932E-2</v>
       </c>
-      <c r="P221">
-        <v>-8</v>
-      </c>
-      <c r="Q221" t="str">
-        <f t="shared" si="3"/>
-        <v>2018-Q2</v>
-      </c>
-    </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
         <v>43221</v>
       </c>
@@ -11002,15 +9444,8 @@
       <c r="O222">
         <v>-1.39660184901516E-2</v>
       </c>
-      <c r="P222">
-        <v>-8.6999999999999993</v>
-      </c>
-      <c r="Q222" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A223" s="4">
         <v>43252</v>
       </c>
@@ -11047,15 +9482,8 @@
       <c r="O223">
         <v>3.4663917772800097E-2</v>
       </c>
-      <c r="P223">
-        <v>-10.5</v>
-      </c>
-      <c r="Q223" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A224" s="4">
         <v>43282</v>
       </c>
@@ -11092,15 +9520,8 @@
       <c r="O224">
         <v>-1.9133808301839701E-2</v>
       </c>
-      <c r="P224">
-        <v>-9.8000000000000007</v>
-      </c>
-      <c r="Q224" t="str">
-        <f t="shared" si="3"/>
-        <v>2018-Q3</v>
-      </c>
-    </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A225" s="4">
         <v>43313</v>
       </c>
@@ -11137,15 +9558,8 @@
       <c r="O225">
         <v>1.5897111227683801E-2</v>
       </c>
-      <c r="P225">
-        <v>-10.4</v>
-      </c>
-      <c r="Q225" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A226" s="4">
         <v>43344</v>
       </c>
@@ -11182,15 +9596,8 @@
       <c r="O226">
         <v>-7.5610371732569306E-2</v>
       </c>
-      <c r="P226">
-        <v>-13.8</v>
-      </c>
-      <c r="Q226" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A227" s="4">
         <v>43374</v>
       </c>
@@ -11227,15 +9634,8 @@
       <c r="O227">
         <v>-1.7731836101708299E-2</v>
       </c>
-      <c r="P227">
-        <v>-11.3</v>
-      </c>
-      <c r="Q227" t="str">
-        <f t="shared" si="3"/>
-        <v>2018-Q4</v>
-      </c>
-    </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A228" s="4">
         <v>43405</v>
       </c>
@@ -11272,15 +9672,8 @@
       <c r="O228">
         <v>-5.6150532796548802E-2</v>
       </c>
-      <c r="P228">
-        <v>-13.6</v>
-      </c>
-      <c r="Q228" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A229" s="4">
         <v>43435</v>
       </c>
@@ -11317,15 +9710,8 @@
       <c r="O229">
         <v>5.3909837610174101E-2</v>
       </c>
-      <c r="P229">
-        <v>-16.899999999999999</v>
-      </c>
-      <c r="Q229" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A230" s="4">
         <v>43466</v>
       </c>
@@ -11362,15 +9748,8 @@
       <c r="O230">
         <v>4.8441702792231901E-2</v>
       </c>
-      <c r="P230">
-        <v>-12.1</v>
-      </c>
-      <c r="Q230" t="str">
-        <f t="shared" si="3"/>
-        <v>2019-Q1</v>
-      </c>
-    </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A231" s="4">
         <v>43497</v>
       </c>
@@ -11407,15 +9786,8 @@
       <c r="O231">
         <v>2.0772984008354801E-2</v>
       </c>
-      <c r="P231">
-        <v>-10.5</v>
-      </c>
-      <c r="Q231" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A232" s="4">
         <v>43525</v>
       </c>
@@ -11452,15 +9824,8 @@
       <c r="O232">
         <v>4.3141309311238302E-2</v>
       </c>
-      <c r="P232">
-        <v>-9.9</v>
-      </c>
-      <c r="Q232" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
         <v>43556</v>
       </c>
@@ -11497,15 +9862,8 @@
       <c r="O233">
         <v>-7.0212055246733102E-2</v>
       </c>
-      <c r="P233">
-        <v>-10.3</v>
-      </c>
-      <c r="Q233" t="str">
-        <f t="shared" si="3"/>
-        <v>2019-Q2</v>
-      </c>
-    </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A234" s="4">
         <v>43586</v>
       </c>
@@ -11542,15 +9900,8 @@
       <c r="O234">
         <v>6.1683766351279701E-2</v>
       </c>
-      <c r="P234">
-        <v>-8.3000000000000007</v>
-      </c>
-      <c r="Q234" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A235" s="4">
         <v>43617</v>
       </c>
@@ -11587,15 +9938,8 @@
       <c r="O235">
         <v>-3.6300543100384899E-3</v>
       </c>
-      <c r="P235">
-        <v>-8.3000000000000007</v>
-      </c>
-      <c r="Q235" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A236" s="4">
         <v>43647</v>
       </c>
@@ -11632,15 +9976,8 @@
       <c r="O236">
         <v>-6.9858625727086104E-3</v>
       </c>
-      <c r="P236">
-        <v>-6.6</v>
-      </c>
-      <c r="Q236" t="str">
-        <f t="shared" si="3"/>
-        <v>2019-Q3</v>
-      </c>
-    </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="237" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A237" s="4">
         <v>43678</v>
       </c>
@@ -11677,15 +10014,8 @@
       <c r="O237">
         <v>3.5369394591752402E-2</v>
       </c>
-      <c r="P237">
-        <v>-7.5</v>
-      </c>
-      <c r="Q237" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="238" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A238" s="4">
         <v>43709</v>
       </c>
@@ -11722,15 +10052,8 @@
       <c r="O238">
         <v>9.1289943647616702E-3</v>
       </c>
-      <c r="P238">
-        <v>-6.1</v>
-      </c>
-      <c r="Q238" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A239" s="4">
         <v>43739</v>
       </c>
@@ -11767,15 +10090,8 @@
       <c r="O239">
         <v>3.0137151409080701E-2</v>
       </c>
-      <c r="P239">
-        <v>-6.6</v>
-      </c>
-      <c r="Q239" t="str">
-        <f t="shared" si="3"/>
-        <v>2019-Q4</v>
-      </c>
-    </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A240" s="4">
         <v>43770</v>
       </c>
@@ -11812,15 +10128,8 @@
       <c r="O240">
         <v>1.2267885247728901E-2</v>
       </c>
-      <c r="P240">
-        <v>-5.8</v>
-      </c>
-      <c r="Q240" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A241" s="4">
         <v>43800</v>
       </c>
@@ -11857,15 +10166,8 @@
       <c r="O241">
         <v>-2.9145713326597499E-2</v>
       </c>
-      <c r="P241">
-        <v>-9.5</v>
-      </c>
-      <c r="Q241" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A242" s="4">
         <v>43831</v>
       </c>
@@ -11902,15 +10204,8 @@
       <c r="O242">
         <v>-8.9377412794403796E-2</v>
       </c>
-      <c r="P242">
-        <v>-8.8000000000000007</v>
-      </c>
-      <c r="Q242" t="str">
-        <f t="shared" si="3"/>
-        <v>2020-Q1</v>
-      </c>
-    </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A243" s="4">
         <v>43862</v>
       </c>
@@ -11947,15 +10242,8 @@
       <c r="O243">
         <v>-0.188850623924395</v>
       </c>
-      <c r="P243">
-        <v>-7.5</v>
-      </c>
-      <c r="Q243" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="244" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
         <v>43891</v>
       </c>
@@ -11992,15 +10280,8 @@
       <c r="O244">
         <v>3.9267793313097599E-2</v>
       </c>
-      <c r="P244">
-        <v>-12.5</v>
-      </c>
-      <c r="Q244" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A245" s="4">
         <v>43922</v>
       </c>
@@ -12037,15 +10318,8 @@
       <c r="O245">
         <v>2.6601658827990701E-2</v>
       </c>
-      <c r="P245">
-        <v>-21.8</v>
-      </c>
-      <c r="Q245" t="str">
-        <f t="shared" si="3"/>
-        <v>2020-Q2</v>
-      </c>
-    </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A246" s="4">
         <v>43952</v>
       </c>
@@ -12082,15 +10356,8 @@
       <c r="O246">
         <v>4.9961495641838397E-2</v>
       </c>
-      <c r="P246">
-        <v>-17.8</v>
-      </c>
-      <c r="Q246" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A247" s="4">
         <v>43983</v>
       </c>
@@ -12127,15 +10394,8 @@
       <c r="O247">
         <v>-3.1341105182971098E-2</v>
       </c>
-      <c r="P247">
-        <v>-12.4</v>
-      </c>
-      <c r="Q247" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A248" s="4">
         <v>44013</v>
       </c>
@@ -12172,15 +10432,8 @@
       <c r="O248">
         <v>3.3613643111712201E-2</v>
       </c>
-      <c r="P248">
-        <v>-11.8</v>
-      </c>
-      <c r="Q248" t="str">
-        <f t="shared" si="3"/>
-        <v>2020-Q3</v>
-      </c>
-    </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A249" s="4">
         <v>44044</v>
       </c>
@@ -12217,15 +10470,8 @@
       <c r="O249">
         <v>-2.94935303814245E-2</v>
       </c>
-      <c r="P249">
-        <v>-12.2</v>
-      </c>
-      <c r="Q249" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="250" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A250" s="4">
         <v>44075</v>
       </c>
@@ -12262,15 +10508,8 @@
       <c r="O250">
         <v>-4.45289197271403E-2</v>
       </c>
-      <c r="P250">
-        <v>-10.9</v>
-      </c>
-      <c r="Q250" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A251" s="4">
         <v>44105</v>
       </c>
@@ -12307,15 +10546,8 @@
       <c r="O251">
         <v>0.183311713258691</v>
       </c>
-      <c r="P251">
-        <v>-13.4</v>
-      </c>
-      <c r="Q251" t="str">
-        <f t="shared" si="3"/>
-        <v>2020-Q4</v>
-      </c>
-    </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="252" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A252" s="4">
         <v>44136</v>
       </c>
@@ -12352,15 +10584,8 @@
       <c r="O252">
         <v>5.9368684612852701E-3</v>
       </c>
-      <c r="P252">
-        <v>-18</v>
-      </c>
-      <c r="Q252" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="253" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A253" s="4">
         <v>44166</v>
       </c>
@@ -12397,15 +10622,8 @@
       <c r="O253">
         <v>-2.7799338355402301E-2</v>
       </c>
-      <c r="P253">
-        <v>-10.8</v>
-      </c>
-      <c r="Q253" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A254" s="4">
         <v>44197</v>
       </c>
@@ -12442,15 +10660,8 @@
       <c r="O254">
         <v>5.4778325952204603E-2</v>
       </c>
-      <c r="P254">
-        <v>-13.6</v>
-      </c>
-      <c r="Q254" t="str">
-        <f t="shared" si="3"/>
-        <v>2021-Q1</v>
-      </c>
-    </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="255" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
         <v>44228</v>
       </c>
@@ -12487,15 +10698,8 @@
       <c r="O255">
         <v>6.1871189738466698E-2</v>
       </c>
-      <c r="P255">
-        <v>-14.2</v>
-      </c>
-      <c r="Q255" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A256" s="4">
         <v>44256</v>
       </c>
@@ -12532,15 +10736,8 @@
       <c r="O256">
         <v>3.2791258453622497E-2</v>
       </c>
-      <c r="P256">
-        <v>-9.8000000000000007</v>
-      </c>
-      <c r="Q256" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="257" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A257" s="4">
         <v>44287</v>
       </c>
@@ -12577,15 +10774,8 @@
       <c r="O257">
         <v>2.7947849235816901E-2</v>
       </c>
-      <c r="P257">
-        <v>-9.8000000000000007</v>
-      </c>
-      <c r="Q257" t="str">
-        <f t="shared" si="3"/>
-        <v>2021-Q2</v>
-      </c>
-    </row>
-    <row r="258" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="258" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A258" s="4">
         <v>44317</v>
       </c>
@@ -12622,15 +10812,8 @@
       <c r="O258">
         <v>9.3648166071691498E-3</v>
       </c>
-      <c r="P258">
-        <v>-5.4</v>
-      </c>
-      <c r="Q258" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="259" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A259" s="4">
         <v>44348</v>
       </c>
@@ -12667,15 +10850,8 @@
       <c r="O259">
         <v>1.5995001115275201E-2</v>
       </c>
-      <c r="P259">
-        <v>-0.2</v>
-      </c>
-      <c r="Q259" t="str">
-        <f t="shared" ref="Q259:Q313" si="4">IF(MONTH($A259) = 1, YEAR($A259)&amp;"-Q"&amp;MONTH($A259), IF(MONTH($A259) = 4, YEAR($A259)&amp;"-Q2", IF(MONTH($A259) = 7, YEAR($A259)&amp;"-Q3", IF(MONTH($A259) = 10, YEAR($A259)&amp;"-Q4",""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="260" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A260" s="4">
         <v>44378</v>
       </c>
@@ -12712,15 +10888,8 @@
       <c r="O260">
         <v>1.0143879167863201E-2</v>
       </c>
-      <c r="P260">
-        <v>-3.1</v>
-      </c>
-      <c r="Q260" t="str">
-        <f t="shared" si="4"/>
-        <v>2021-Q3</v>
-      </c>
-    </row>
-    <row r="261" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="261" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A261" s="4">
         <v>44409</v>
       </c>
@@ -12757,15 +10926,8 @@
       <c r="O261">
         <v>-2.42690858744634E-2</v>
       </c>
-      <c r="P261">
-        <v>-6.5</v>
-      </c>
-      <c r="Q261" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="262" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A262" s="4">
         <v>44440</v>
       </c>
@@ -12802,15 +10964,8 @@
       <c r="O262">
         <v>4.6498556115810899E-2</v>
       </c>
-      <c r="P262">
-        <v>-2.8</v>
-      </c>
-      <c r="Q262" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="263" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A263" s="4">
         <v>44470</v>
       </c>
@@ -12847,15 +11002,8 @@
       <c r="O263">
         <v>-1.6113647915297201E-2</v>
       </c>
-      <c r="P263">
-        <v>-6.2</v>
-      </c>
-      <c r="Q263" t="str">
-        <f t="shared" si="4"/>
-        <v>2021-Q4</v>
-      </c>
-    </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="264" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A264" s="4">
         <v>44501</v>
       </c>
@@ -12892,15 +11040,8 @@
       <c r="O264">
         <v>6.2275231193361001E-2</v>
       </c>
-      <c r="P264">
-        <v>-6.9</v>
-      </c>
-      <c r="Q264" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="265" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A265" s="4">
         <v>44531</v>
       </c>
@@ -12937,15 +11078,8 @@
       <c r="O265">
         <v>-2.1740128411668301E-2</v>
       </c>
-      <c r="P265">
-        <v>-8.5</v>
-      </c>
-      <c r="Q265" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="266" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
         <v>44562</v>
       </c>
@@ -12982,15 +11116,8 @@
       <c r="O266">
         <v>-4.9852079538506899E-2</v>
       </c>
-      <c r="P266">
-        <v>-9.4</v>
-      </c>
-      <c r="Q266" t="str">
-        <f t="shared" si="4"/>
-        <v>2022-Q1</v>
-      </c>
-    </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="267" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A267" s="4">
         <v>44593</v>
       </c>
@@ -13027,15 +11154,8 @@
       <c r="O267">
         <v>1.5617726194960799E-4</v>
       </c>
-      <c r="P267">
-        <v>-8.5</v>
-      </c>
-      <c r="Q267" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="268" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A268" s="4">
         <v>44621</v>
       </c>
@@ -13072,15 +11192,8 @@
       <c r="O268">
         <v>-1.9115867379476001E-2</v>
       </c>
-      <c r="P268">
-        <v>-21.2</v>
-      </c>
-      <c r="Q268" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="269" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A269" s="4">
         <v>44652</v>
       </c>
@@ -13117,15 +11230,8 @@
       <c r="O269">
         <v>-9.9935253474932005E-3</v>
       </c>
-      <c r="P269">
-        <v>-19.3</v>
-      </c>
-      <c r="Q269" t="str">
-        <f t="shared" si="4"/>
-        <v>2022-Q2</v>
-      </c>
-    </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="270" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A270" s="4">
         <v>44682</v>
       </c>
@@ -13162,15 +11268,8 @@
       <c r="O270">
         <v>-8.8171172449726498E-2</v>
       </c>
-      <c r="P270">
-        <v>-18.899999999999999</v>
-      </c>
-      <c r="Q270" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="271" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A271" s="4">
         <v>44713</v>
       </c>
@@ -13207,15 +11306,8 @@
       <c r="O271">
         <v>8.5028128360670904E-2</v>
       </c>
-      <c r="P271">
-        <v>-21.2</v>
-      </c>
-      <c r="Q271" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="272" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A272" s="4">
         <v>44743</v>
       </c>
@@ -13252,15 +11344,8 @@
       <c r="O272">
         <v>-5.1452446850566602E-2</v>
       </c>
-      <c r="P272">
-        <v>-21.8</v>
-      </c>
-      <c r="Q272" t="str">
-        <f t="shared" si="4"/>
-        <v>2022-Q3</v>
-      </c>
-    </row>
-    <row r="273" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="273" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A273" s="4">
         <v>44774</v>
       </c>
@@ -13297,15 +11382,8 @@
       <c r="O273">
         <v>-6.10514836768523E-2</v>
       </c>
-      <c r="P273">
-        <v>-18.8</v>
-      </c>
-      <c r="Q273" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="274" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="274" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A274" s="4">
         <v>44805</v>
       </c>
@@ -13342,15 +11420,8 @@
       <c r="O274">
         <v>8.3917458415294605E-2</v>
       </c>
-      <c r="P274">
-        <v>-22.3</v>
-      </c>
-      <c r="Q274" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="275" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="275" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A275" s="4">
         <v>44835</v>
       </c>
@@ -13387,15 +11458,8 @@
       <c r="O275">
         <v>7.2583665753983298E-2</v>
       </c>
-      <c r="P275">
-        <v>-20.8</v>
-      </c>
-      <c r="Q275" t="str">
-        <f t="shared" si="4"/>
-        <v>2022-Q4</v>
-      </c>
-    </row>
-    <row r="276" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="276" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A276" s="4">
         <v>44866</v>
       </c>
@@ -13432,15 +11496,8 @@
       <c r="O276">
         <v>-4.0087692013493402E-2</v>
       </c>
-      <c r="P276">
-        <v>-18.7</v>
-      </c>
-      <c r="Q276" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="277" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="277" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
         <v>44896</v>
       </c>
@@ -13477,15 +11534,8 @@
       <c r="O277">
         <v>8.9858598930707204E-2</v>
       </c>
-      <c r="P277">
-        <v>-20.6</v>
-      </c>
-      <c r="Q277" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="278" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="278" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A278" s="4">
         <v>44927</v>
       </c>
@@ -13522,15 +11572,8 @@
       <c r="O278">
         <v>2.5855897231718199E-2</v>
       </c>
-      <c r="P278">
-        <v>-20.5</v>
-      </c>
-      <c r="Q278" t="str">
-        <f t="shared" si="4"/>
-        <v>2023-Q1</v>
-      </c>
-    </row>
-    <row r="279" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="279" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A279" s="4">
         <v>44958</v>
       </c>
@@ -13567,15 +11610,8 @@
       <c r="O279">
         <v>7.4652526732705803E-3</v>
       </c>
-      <c r="P279">
-        <v>-21.4</v>
-      </c>
-      <c r="Q279" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="280" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="280" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A280" s="4">
         <v>44986</v>
       </c>
@@ -13612,15 +11648,8 @@
       <c r="O280">
         <v>2.2832248414690798E-2</v>
       </c>
-      <c r="P280">
-        <v>-20.6</v>
-      </c>
-      <c r="Q280" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="281" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="281" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A281" s="4">
         <v>45017</v>
       </c>
@@ -13657,15 +11686,8 @@
       <c r="O281">
         <v>-5.3857348296094898E-2</v>
       </c>
-      <c r="P281">
-        <v>-19</v>
-      </c>
-      <c r="Q281" t="str">
-        <f t="shared" si="4"/>
-        <v>2023-Q2</v>
-      </c>
-    </row>
-    <row r="282" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="282" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A282" s="4">
         <v>45047</v>
       </c>
@@ -13702,15 +11724,8 @@
       <c r="O282">
         <v>4.1576419998405001E-2</v>
       </c>
-      <c r="P282">
-        <v>-17.100000000000001</v>
-      </c>
-      <c r="Q282" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="283" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="283" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A283" s="4">
         <v>45078</v>
       </c>
@@ -13747,15 +11762,8 @@
       <c r="O283">
         <v>1.3118831867929601E-2</v>
       </c>
-      <c r="P283">
-        <v>-14.8</v>
-      </c>
-      <c r="Q283" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="284" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="284" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A284" s="4">
         <v>45108</v>
       </c>
@@ -13792,15 +11800,8 @@
       <c r="O284">
         <v>-2.44475147258836E-2</v>
       </c>
-      <c r="P284">
-        <v>-14.1</v>
-      </c>
-      <c r="Q284" t="str">
-        <f t="shared" si="4"/>
-        <v>2023-Q3</v>
-      </c>
-    </row>
-    <row r="285" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="285" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A285" s="4">
         <v>45139</v>
       </c>
@@ -13837,15 +11838,8 @@
       <c r="O285">
         <v>-2.51387649897108E-2</v>
       </c>
-      <c r="P285">
-        <v>-14.8</v>
-      </c>
-      <c r="Q285" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="286" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="286" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A286" s="4">
         <v>45170</v>
       </c>
@@ -13882,15 +11876,8 @@
       <c r="O286">
         <v>-3.5581146680208099E-2</v>
       </c>
-      <c r="P286">
-        <v>-15.8</v>
-      </c>
-      <c r="Q286" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="287" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="287" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A287" s="4">
         <v>45200</v>
       </c>
@@ -13927,15 +11914,8 @@
       <c r="O287">
         <v>5.9909084367721001E-2</v>
       </c>
-      <c r="P287">
-        <v>-16.7</v>
-      </c>
-      <c r="Q287" t="str">
-        <f t="shared" si="4"/>
-        <v>2023-Q4</v>
-      </c>
-    </row>
-    <row r="288" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="288" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
         <v>45231</v>
       </c>
@@ -13972,15 +11952,8 @@
       <c r="O288">
         <v>3.12952610312962E-2</v>
       </c>
-      <c r="P288">
-        <v>-13.5</v>
-      </c>
-      <c r="Q288" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="289" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="289" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A289" s="4">
         <v>45261</v>
       </c>
@@ -14017,15 +11990,8 @@
       <c r="O289">
         <v>1.4943744660580899E-2</v>
       </c>
-      <c r="P289">
-        <v>-13.4</v>
-      </c>
-      <c r="Q289" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="290" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="290" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A290" s="4">
         <v>45292</v>
       </c>
@@ -14062,15 +12028,8 @@
       <c r="O290">
         <v>3.4741307808008798E-2</v>
       </c>
-      <c r="P290">
-        <v>-11.6</v>
-      </c>
-      <c r="Q290" t="str">
-        <f t="shared" si="4"/>
-        <v>2024-Q1</v>
-      </c>
-    </row>
-    <row r="291" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="291" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A291" s="4">
         <v>45323</v>
       </c>
@@ -14107,15 +12066,8 @@
       <c r="O291">
         <v>3.4513468055111601E-2</v>
       </c>
-      <c r="P291">
-        <v>-14.6</v>
-      </c>
-      <c r="Q291" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="292" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="292" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A292" s="4">
         <v>45352</v>
       </c>
@@ -14152,15 +12104,8 @@
       <c r="O292">
         <v>-2.7286350392611101E-2</v>
       </c>
-      <c r="P292">
-        <v>-13.4</v>
-      </c>
-      <c r="Q292" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="293" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="293" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A293" s="4">
         <v>45383</v>
       </c>
@@ -14197,15 +12142,8 @@
       <c r="O293">
         <v>9.9387173631271296E-4</v>
       </c>
-      <c r="P293">
-        <v>-15.6</v>
-      </c>
-      <c r="Q293" t="str">
-        <f t="shared" si="4"/>
-        <v>2024-Q2</v>
-      </c>
-    </row>
-    <row r="294" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="294" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A294" s="4">
         <v>45413</v>
       </c>
@@ -14242,15 +12180,8 @@
       <c r="O294">
         <v>-6.6397347133280604E-2</v>
       </c>
-      <c r="P294">
-        <v>-13.7</v>
-      </c>
-      <c r="Q294" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="295" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="295" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A295" s="4">
         <v>45444</v>
       </c>
@@ -14287,15 +12218,8 @@
       <c r="O295">
         <v>6.9403667137972703E-3</v>
       </c>
-      <c r="P295">
-        <v>-14.4</v>
-      </c>
-      <c r="Q295" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="296" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="296" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A296" s="4">
         <v>45474</v>
       </c>
@@ -14332,15 +12256,8 @@
       <c r="O296">
         <v>1.3119443137172801E-2</v>
       </c>
-      <c r="P296">
-        <v>-15.3</v>
-      </c>
-      <c r="Q296" t="str">
-        <f t="shared" si="4"/>
-        <v>2024-Q3</v>
-      </c>
-    </row>
-    <row r="297" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="297" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A297" s="4">
         <v>45505</v>
       </c>
@@ -14377,15 +12294,8 @@
       <c r="O297">
         <v>6.2879401366799904E-4</v>
       </c>
-      <c r="P297">
-        <v>-12.9</v>
-      </c>
-      <c r="Q297" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="298" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="298" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A298" s="4">
         <v>45536</v>
       </c>
@@ -14422,15 +12332,8 @@
       <c r="O298">
         <v>-3.80904976364249E-2</v>
       </c>
-      <c r="P298">
-        <v>-11.5</v>
-      </c>
-      <c r="Q298" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="299" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="299" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
         <v>45566</v>
       </c>
@@ -14467,15 +12370,8 @@
       <c r="O299">
         <v>-1.5805123095475399E-2</v>
       </c>
-      <c r="P299">
-        <v>-12.8</v>
-      </c>
-      <c r="Q299" t="str">
-        <f t="shared" si="4"/>
-        <v>2024-Q4</v>
-      </c>
-    </row>
-    <row r="300" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="300" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A300" s="4">
         <v>45597</v>
       </c>
@@ -14512,15 +12408,8 @@
       <c r="O300">
         <v>1.9928391401858599E-2</v>
       </c>
-      <c r="P300">
-        <v>-15.2</v>
-      </c>
-      <c r="Q300" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="301" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="301" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A301" s="4">
         <v>45627</v>
       </c>
@@ -14557,15 +12446,8 @@
       <c r="O301">
         <v>7.4319365915343397E-2</v>
       </c>
-      <c r="P301">
-        <v>-17.7</v>
-      </c>
-      <c r="Q301" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="302" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="302" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A302" s="4">
         <v>45658</v>
       </c>
@@ -14602,15 +12484,8 @@
       <c r="O302">
         <v>2.01055176633229E-2</v>
       </c>
-      <c r="P302">
-        <v>-14</v>
-      </c>
-      <c r="Q302" t="str">
-        <f t="shared" si="4"/>
-        <v>2025-Q1</v>
-      </c>
-    </row>
-    <row r="303" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="303" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A303" s="4">
         <v>45689</v>
       </c>
@@ -14647,15 +12522,8 @@
       <c r="O303">
         <v>-4.0366826716081099E-2</v>
       </c>
-      <c r="P303">
-        <v>-13</v>
-      </c>
-      <c r="Q303" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="304" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="304" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A304" s="4">
         <v>45717</v>
       </c>
@@ -14692,15 +12560,8 @@
       <c r="O304">
         <v>-2.55906348888661E-2</v>
       </c>
-      <c r="P304">
-        <v>-14.8</v>
-      </c>
-      <c r="Q304" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="305" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="305" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A305" s="4">
         <v>45748</v>
       </c>
@@ -14737,15 +12598,8 @@
       <c r="O305">
         <v>2.0595343921179701E-2</v>
       </c>
-      <c r="P305">
-        <v>-16.600000000000001</v>
-      </c>
-      <c r="Q305" t="str">
-        <f t="shared" si="4"/>
-        <v>2025-Q2</v>
-      </c>
-    </row>
-    <row r="306" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="306" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A306" s="4">
         <v>45778</v>
       </c>
@@ -14782,15 +12636,8 @@
       <c r="O306">
         <v>-1.11534551175581E-2</v>
       </c>
-      <c r="P306">
-        <v>-17.600000000000001</v>
-      </c>
-      <c r="Q306" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="307" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="307" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A307" s="4">
         <v>45809</v>
       </c>
@@ -14827,15 +12674,8 @@
       <c r="O307">
         <v>1.37404520202828E-2</v>
       </c>
-      <c r="P307">
-        <v>-17.5</v>
-      </c>
-      <c r="Q307" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="308" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="308" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A308" s="4">
         <v>45839</v>
       </c>
@@ -14872,15 +12712,8 @@
       <c r="O308">
         <v>-8.7970176754783597E-3</v>
       </c>
-      <c r="P308">
-        <v>-16.8</v>
-      </c>
-      <c r="Q308" t="str">
-        <f t="shared" si="4"/>
-        <v>2025-Q3</v>
-      </c>
-    </row>
-    <row r="309" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="309" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A309" s="4">
         <v>45870</v>
       </c>
@@ -14917,15 +12750,8 @@
       <c r="O309">
         <v>2.4622014431990601E-2</v>
       </c>
-      <c r="P309">
-        <v>-18.5</v>
-      </c>
-      <c r="Q309" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="310" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="310" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
         <v>45901</v>
       </c>
@@ -14962,15 +12788,8 @@
       <c r="O310">
         <v>2.8113201348792999E-2</v>
       </c>
-      <c r="P310">
-        <v>-19.3</v>
-      </c>
-      <c r="Q310" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="311" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="311" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A311" s="4">
         <v>45931</v>
       </c>
@@ -15007,15 +12826,8 @@
       <c r="O311">
         <v>2.01940280652124E-4</v>
       </c>
-      <c r="P311">
-        <v>-15.5</v>
-      </c>
-      <c r="Q311" t="str">
-        <f t="shared" si="4"/>
-        <v>2025-Q4</v>
-      </c>
-    </row>
-    <row r="312" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="312" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A312" s="4">
         <v>45962</v>
       </c>
@@ -15052,15 +12864,8 @@
       <c r="O312">
         <v>3.2927381507334998E-3</v>
       </c>
-      <c r="P312">
-        <v>-15.8</v>
-      </c>
-      <c r="Q312" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="313" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="313" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A313" s="4">
         <v>45992</v>
       </c>
@@ -15097,15 +12902,8 @@
       <c r="O313">
         <v>1.14647629338211E-2</v>
       </c>
-      <c r="P313">
-        <v>-16.2</v>
-      </c>
-      <c r="Q313" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="314" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="314" spans="1:15" x14ac:dyDescent="0.2">
       <c r="I314" s="6"/>
     </row>
   </sheetData>
@@ -15117,41 +12915,41 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D49BF3C-99BE-B04B-9A3C-656750B962CB}">
   <dimension ref="A1:Q313"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>5</v>
@@ -15163,16 +12961,16 @@
         <v>3</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>36526</v>
       </c>
@@ -15219,7 +13017,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>36557</v>
       </c>
@@ -15266,7 +13064,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>36586</v>
       </c>
@@ -15313,7 +13111,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>36617</v>
       </c>
@@ -15360,7 +13158,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>36647</v>
       </c>
@@ -15407,7 +13205,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>36678</v>
       </c>
@@ -15454,7 +13252,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>36708</v>
       </c>
@@ -15501,7 +13299,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>36739</v>
       </c>
@@ -15548,7 +13346,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>36770</v>
       </c>
@@ -15592,10 +13390,10 @@
         <v>69.62</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>36800</v>
       </c>
@@ -15642,7 +13440,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>36831</v>
       </c>
@@ -15689,7 +13487,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>36861</v>
       </c>
@@ -15736,7 +13534,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>36892</v>
       </c>
@@ -15783,7 +13581,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>36923</v>
       </c>
@@ -15830,7 +13628,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>36951</v>
       </c>
@@ -15877,7 +13675,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>36982</v>
       </c>
@@ -15924,7 +13722,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>37012</v>
       </c>
@@ -15971,7 +13769,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>37043</v>
       </c>
@@ -16018,7 +13816,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>37073</v>
       </c>
@@ -16065,7 +13863,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>37104</v>
       </c>
@@ -16112,7 +13910,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>37135</v>
       </c>
@@ -16159,7 +13957,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>37165</v>
       </c>
@@ -16206,7 +14004,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>37196</v>
       </c>
@@ -16253,7 +14051,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>37226</v>
       </c>
@@ -16300,7 +14098,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>37257</v>
       </c>
@@ -16347,7 +14145,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>37288</v>
       </c>
@@ -16394,7 +14192,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>37316</v>
       </c>
@@ -16420,7 +14218,7 @@
         <v>#N/A</v>
       </c>
       <c r="I28">
-        <v>0.48942947387695313</v>
+        <v>0.48942947387695312</v>
       </c>
       <c r="L28">
         <v>111.8</v>
@@ -16441,7 +14239,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>37347</v>
       </c>
@@ -16488,7 +14286,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>37377</v>
       </c>
@@ -16535,7 +14333,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>37408</v>
       </c>
@@ -16582,7 +14380,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>37438</v>
       </c>
@@ -16629,7 +14427,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>37469</v>
       </c>
@@ -16676,7 +14474,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>37500</v>
       </c>
@@ -16723,7 +14521,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>37530</v>
       </c>
@@ -16770,7 +14568,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>37561</v>
       </c>
@@ -16817,7 +14615,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>37591</v>
       </c>
@@ -16864,7 +14662,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>37622</v>
       </c>
@@ -16911,7 +14709,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>37653</v>
       </c>
@@ -16958,7 +14756,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>37681</v>
       </c>
@@ -17005,7 +14803,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>37712</v>
       </c>
@@ -17052,7 +14850,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>37742</v>
       </c>
@@ -17099,7 +14897,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>37773</v>
       </c>
@@ -17146,7 +14944,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>37803</v>
       </c>
@@ -17193,7 +14991,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>37834</v>
       </c>
@@ -17240,7 +15038,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>37865</v>
       </c>
@@ -17287,7 +15085,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>37895</v>
       </c>
@@ -17334,7 +15132,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>37926</v>
       </c>
@@ -17381,7 +15179,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>37956</v>
       </c>
@@ -17428,7 +15226,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>37987</v>
       </c>
@@ -17475,7 +15273,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>38018</v>
       </c>
@@ -17522,7 +15320,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>38047</v>
       </c>
@@ -17569,7 +15367,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>38078</v>
       </c>
@@ -17616,7 +15414,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>38108</v>
       </c>
@@ -17663,7 +15461,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>38139</v>
       </c>
@@ -17710,7 +15508,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>38169</v>
       </c>
@@ -17757,7 +15555,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>38200</v>
       </c>
@@ -17804,7 +15602,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>38231</v>
       </c>
@@ -17851,7 +15649,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>38261</v>
       </c>
@@ -17898,7 +15696,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <v>38292</v>
       </c>
@@ -17945,7 +15743,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <v>38322</v>
       </c>
@@ -17992,7 +15790,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>38353</v>
       </c>
@@ -18039,7 +15837,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <v>38384</v>
       </c>
@@ -18086,7 +15884,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>38412</v>
       </c>
@@ -18133,7 +15931,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>38443</v>
       </c>
@@ -18180,7 +15978,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
         <v>38473</v>
       </c>
@@ -18227,7 +16025,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>38504</v>
       </c>
@@ -18274,7 +16072,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
         <v>38534</v>
       </c>
@@ -18321,7 +16119,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
         <v>38565</v>
       </c>
@@ -18368,7 +16166,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
         <v>38596</v>
       </c>
@@ -18415,7 +16213,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
         <v>38626</v>
       </c>
@@ -18462,7 +16260,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>38657</v>
       </c>
@@ -18506,10 +16304,10 @@
         <v>78.59</v>
       </c>
       <c r="Q72" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>38687</v>
       </c>
@@ -18556,7 +16354,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
         <v>38718</v>
       </c>
@@ -18603,7 +16401,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
         <v>38749</v>
       </c>
@@ -18650,7 +16448,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
         <v>38777</v>
       </c>
@@ -18697,7 +16495,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
         <v>38808</v>
       </c>
@@ -18744,7 +16542,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
         <v>38838</v>
       </c>
@@ -18791,7 +16589,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
         <v>38869</v>
       </c>
@@ -18838,7 +16636,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
         <v>38899</v>
       </c>
@@ -18885,7 +16683,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
         <v>38930</v>
       </c>
@@ -18932,7 +16730,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
         <v>38961</v>
       </c>
@@ -18979,7 +16777,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
         <v>38991</v>
       </c>
@@ -19026,7 +16824,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
         <v>39022</v>
       </c>
@@ -19073,7 +16871,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
         <v>39052</v>
       </c>
@@ -19120,7 +16918,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
         <v>39083</v>
       </c>
@@ -19167,7 +16965,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
         <v>39114</v>
       </c>
@@ -19214,7 +17012,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A88" s="4">
         <v>39142</v>
       </c>
@@ -19261,7 +17059,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A89" s="4">
         <v>39173</v>
       </c>
@@ -19308,7 +17106,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
         <v>39203</v>
       </c>
@@ -19355,7 +17153,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A91" s="4">
         <v>39234</v>
       </c>
@@ -19402,7 +17200,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A92" s="4">
         <v>39264</v>
       </c>
@@ -19449,7 +17247,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A93" s="4">
         <v>39295</v>
       </c>
@@ -19496,7 +17294,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A94" s="4">
         <v>39326</v>
       </c>
@@ -19543,7 +17341,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A95" s="4">
         <v>39356</v>
       </c>
@@ -19590,7 +17388,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A96" s="4">
         <v>39387</v>
       </c>
@@ -19637,7 +17435,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A97" s="4">
         <v>39417</v>
       </c>
@@ -19684,7 +17482,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A98" s="4">
         <v>39448</v>
       </c>
@@ -19731,7 +17529,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A99" s="4">
         <v>39479</v>
       </c>
@@ -19778,7 +17576,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A100" s="4">
         <v>39508</v>
       </c>
@@ -19825,7 +17623,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
         <v>39539</v>
       </c>
@@ -19872,7 +17670,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A102" s="4">
         <v>39569</v>
       </c>
@@ -19919,7 +17717,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A103" s="4">
         <v>39600</v>
       </c>
@@ -19966,7 +17764,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A104" s="4">
         <v>39630</v>
       </c>
@@ -20013,7 +17811,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A105" s="4">
         <v>39661</v>
       </c>
@@ -20060,7 +17858,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A106" s="4">
         <v>39692</v>
       </c>
@@ -20107,7 +17905,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A107" s="4">
         <v>39722</v>
       </c>
@@ -20154,7 +17952,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A108" s="4">
         <v>39753</v>
       </c>
@@ -20201,7 +17999,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A109" s="4">
         <v>39783</v>
       </c>
@@ -20248,7 +18046,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A110" s="4">
         <v>39814</v>
       </c>
@@ -20295,7 +18093,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A111" s="4">
         <v>39845</v>
       </c>
@@ -20342,7 +18140,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
         <v>39873</v>
       </c>
@@ -20389,7 +18187,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A113" s="4">
         <v>39904</v>
       </c>
@@ -20436,7 +18234,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A114" s="4">
         <v>39934</v>
       </c>
@@ -20483,7 +18281,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A115" s="4">
         <v>39965</v>
       </c>
@@ -20530,7 +18328,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A116" s="4">
         <v>39995</v>
       </c>
@@ -20577,7 +18375,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A117" s="4">
         <v>40026</v>
       </c>
@@ -20624,7 +18422,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A118" s="4">
         <v>40057</v>
       </c>
@@ -20671,7 +18469,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A119" s="4">
         <v>40087</v>
       </c>
@@ -20718,7 +18516,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A120" s="4">
         <v>40118</v>
       </c>
@@ -20765,7 +18563,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A121" s="4">
         <v>40148</v>
       </c>
@@ -20812,7 +18610,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A122" s="4">
         <v>40179</v>
       </c>
@@ -20859,7 +18657,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
         <v>40210</v>
       </c>
@@ -20906,7 +18704,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A124" s="4">
         <v>40238</v>
       </c>
@@ -20953,7 +18751,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A125" s="4">
         <v>40269</v>
       </c>
@@ -21000,7 +18798,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A126" s="4">
         <v>40299</v>
       </c>
@@ -21047,7 +18845,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A127" s="4">
         <v>40330</v>
       </c>
@@ -21094,7 +18892,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A128" s="4">
         <v>40360</v>
       </c>
@@ -21141,7 +18939,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A129" s="4">
         <v>40391</v>
       </c>
@@ -21188,7 +18986,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A130" s="4">
         <v>40422</v>
       </c>
@@ -21235,7 +19033,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A131" s="4">
         <v>40452</v>
       </c>
@@ -21282,7 +19080,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A132" s="4">
         <v>40483</v>
       </c>
@@ -21329,7 +19127,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A133" s="4">
         <v>40513</v>
       </c>
@@ -21376,7 +19174,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
         <v>40544</v>
       </c>
@@ -21423,7 +19221,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A135" s="4">
         <v>40575</v>
       </c>
@@ -21470,7 +19268,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A136" s="4">
         <v>40603</v>
       </c>
@@ -21517,7 +19315,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A137" s="4">
         <v>40634</v>
       </c>
@@ -21564,7 +19362,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A138" s="4">
         <v>40664</v>
       </c>
@@ -21611,7 +19409,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A139" s="4">
         <v>40695</v>
       </c>
@@ -21658,7 +19456,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A140" s="4">
         <v>40725</v>
       </c>
@@ -21702,10 +19500,10 @@
         <v>98.81</v>
       </c>
       <c r="Q140" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A141" s="4">
         <v>40756</v>
       </c>
@@ -21752,7 +19550,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A142" s="4">
         <v>40787</v>
       </c>
@@ -21799,7 +19597,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A143" s="4">
         <v>40817</v>
       </c>
@@ -21846,7 +19644,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A144" s="4">
         <v>40848</v>
       </c>
@@ -21890,10 +19688,10 @@
         <v>101.58</v>
       </c>
       <c r="Q144" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
         <v>40878</v>
       </c>
@@ -21937,10 +19735,10 @@
         <v>101.53</v>
       </c>
       <c r="Q145" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A146" s="4">
         <v>40909</v>
       </c>
@@ -21984,10 +19782,10 @@
         <v>103.85</v>
       </c>
       <c r="Q146" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A147" s="4">
         <v>40940</v>
       </c>
@@ -22031,10 +19829,10 @@
         <v>104.97</v>
       </c>
       <c r="Q147" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A148" s="4">
         <v>40969</v>
       </c>
@@ -22081,7 +19879,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A149" s="4">
         <v>41000</v>
       </c>
@@ -22125,10 +19923,10 @@
         <v>106.3</v>
       </c>
       <c r="Q149" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A150" s="4">
         <v>41030</v>
       </c>
@@ -22172,10 +19970,10 @@
         <v>104.18</v>
       </c>
       <c r="Q150" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A151" s="4">
         <v>41061</v>
       </c>
@@ -22222,7 +20020,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A152" s="4">
         <v>41091</v>
       </c>
@@ -22266,10 +20064,10 @@
         <v>102.34</v>
       </c>
       <c r="Q152" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A153" s="4">
         <v>41122</v>
       </c>
@@ -22313,10 +20111,10 @@
         <v>105.89</v>
       </c>
       <c r="Q153" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A154" s="4">
         <v>41153</v>
       </c>
@@ -22363,7 +20161,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A155" s="4">
         <v>41183</v>
       </c>
@@ -22410,7 +20208,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
         <v>41214</v>
       </c>
@@ -22454,10 +20252,10 @@
         <v>104.43</v>
       </c>
       <c r="Q156" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A157" s="4">
         <v>41244</v>
       </c>
@@ -22504,7 +20302,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A158" s="4">
         <v>41275</v>
       </c>
@@ -22551,7 +20349,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A159" s="4">
         <v>41306</v>
       </c>
@@ -22598,7 +20396,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A160" s="4">
         <v>41334</v>
       </c>
@@ -22642,10 +20440,10 @@
         <v>107.44</v>
       </c>
       <c r="Q160" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A161" s="4">
         <v>41365</v>
       </c>
@@ -22692,7 +20490,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A162" s="4">
         <v>41395</v>
       </c>
@@ -22736,10 +20534,10 @@
         <v>103.9</v>
       </c>
       <c r="Q162" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A163" s="4">
         <v>41426</v>
       </c>
@@ -22783,10 +20581,10 @@
         <v>103.92</v>
       </c>
       <c r="Q163" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A164" s="4">
         <v>41456</v>
       </c>
@@ -22830,10 +20628,10 @@
         <v>104.23</v>
       </c>
       <c r="Q164" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A165" s="4">
         <v>41487</v>
       </c>
@@ -22877,10 +20675,10 @@
         <v>105.66</v>
       </c>
       <c r="Q165" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A166" s="4">
         <v>41518</v>
       </c>
@@ -22927,7 +20725,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
         <v>41548</v>
       </c>
@@ -22971,10 +20769,10 @@
         <v>105.31</v>
       </c>
       <c r="Q167" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A168" s="4">
         <v>41579</v>
       </c>
@@ -23018,10 +20816,10 @@
         <v>104.68</v>
       </c>
       <c r="Q168" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A169" s="4">
         <v>41609</v>
       </c>
@@ -23065,10 +20863,10 @@
         <v>105.43</v>
       </c>
       <c r="Q169" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A170" s="4">
         <v>41640</v>
       </c>
@@ -23112,10 +20910,10 @@
         <v>106.31</v>
       </c>
       <c r="Q170" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A171" s="4">
         <v>41671</v>
       </c>
@@ -23162,7 +20960,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A172" s="4">
         <v>41699</v>
       </c>
@@ -23206,10 +21004,10 @@
         <v>105.79</v>
       </c>
       <c r="Q172" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A173" s="4">
         <v>41730</v>
       </c>
@@ -23253,10 +21051,10 @@
         <v>105.63</v>
       </c>
       <c r="Q173" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A174" s="4">
         <v>41760</v>
       </c>
@@ -23300,10 +21098,10 @@
         <v>104.99</v>
       </c>
       <c r="Q174" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A175" s="4">
         <v>41791</v>
       </c>
@@ -23347,10 +21145,10 @@
         <v>104.94</v>
       </c>
       <c r="Q175" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A176" s="4">
         <v>41821</v>
       </c>
@@ -23394,10 +21192,10 @@
         <v>105.07</v>
       </c>
       <c r="Q176" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A177" s="4">
         <v>41852</v>
       </c>
@@ -23441,10 +21239,10 @@
         <v>104.23</v>
       </c>
       <c r="Q177" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
         <v>41883</v>
       </c>
@@ -23488,10 +21286,10 @@
         <v>104.01</v>
       </c>
       <c r="Q178" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A179" s="4">
         <v>41913</v>
       </c>
@@ -23535,10 +21333,10 @@
         <v>104.25</v>
       </c>
       <c r="Q179" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A180" s="4">
         <v>41944</v>
       </c>
@@ -23585,7 +21383,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A181" s="4">
         <v>41974</v>
       </c>
@@ -23632,7 +21430,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A182" s="4">
         <v>42005</v>
       </c>
@@ -23679,7 +21477,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A183" s="4">
         <v>42036</v>
       </c>
@@ -23726,7 +21524,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A184" s="4">
         <v>42064</v>
       </c>
@@ -23773,7 +21571,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A185" s="4">
         <v>42095</v>
       </c>
@@ -23820,7 +21618,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A186" s="4">
         <v>42125</v>
       </c>
@@ -23867,7 +21665,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A187" s="4">
         <v>42156</v>
       </c>
@@ -23914,7 +21712,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A188" s="4">
         <v>42186</v>
       </c>
@@ -23961,7 +21759,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
         <v>42217</v>
       </c>
@@ -24008,7 +21806,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A190" s="4">
         <v>42248</v>
       </c>
@@ -24052,10 +21850,10 @@
         <v>98.13</v>
       </c>
       <c r="Q190" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A191" s="4">
         <v>42278</v>
       </c>
@@ -24102,7 +21900,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A192" s="4">
         <v>42309</v>
       </c>
@@ -24149,7 +21947,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A193" s="4">
         <v>42339</v>
       </c>
@@ -24193,10 +21991,10 @@
         <v>96.53</v>
       </c>
       <c r="Q193" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="194" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A194" s="4">
         <v>42370</v>
       </c>
@@ -24243,7 +22041,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A195" s="4">
         <v>42401</v>
       </c>
@@ -24290,7 +22088,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A196" s="4">
         <v>42430</v>
       </c>
@@ -24337,7 +22135,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A197" s="4">
         <v>42461</v>
       </c>
@@ -24384,7 +22182,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A198" s="4">
         <v>42491</v>
       </c>
@@ -24431,7 +22229,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A199" s="4">
         <v>42522</v>
       </c>
@@ -24475,10 +22273,10 @@
         <v>99.55</v>
       </c>
       <c r="Q199" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="200" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
         <v>42552</v>
       </c>
@@ -24522,10 +22320,10 @@
         <v>98.26</v>
       </c>
       <c r="Q200" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="201" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A201" s="4">
         <v>42583</v>
       </c>
@@ -24572,7 +22370,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A202" s="4">
         <v>42614</v>
       </c>
@@ -24619,7 +22417,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A203" s="4">
         <v>42644</v>
       </c>
@@ -24663,10 +22461,10 @@
         <v>98.72</v>
       </c>
       <c r="Q203" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="204" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A204" s="4">
         <v>42675</v>
       </c>
@@ -24713,7 +22511,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A205" s="4">
         <v>42705</v>
       </c>
@@ -24757,10 +22555,10 @@
         <v>100.5</v>
       </c>
       <c r="Q205" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="206" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A206" s="4">
         <v>42736</v>
       </c>
@@ -24807,7 +22605,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A207" s="4">
         <v>42767</v>
       </c>
@@ -24854,7 +22652,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A208" s="4">
         <v>42795</v>
       </c>
@@ -24898,10 +22696,10 @@
         <v>104.5</v>
       </c>
       <c r="Q208" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="209" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A209" s="4">
         <v>42826</v>
       </c>
@@ -24948,7 +22746,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A210" s="4">
         <v>42856</v>
       </c>
@@ -24992,10 +22790,10 @@
         <v>102.61</v>
       </c>
       <c r="Q210" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.4">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="211" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
         <v>42887</v>
       </c>
@@ -25039,10 +22837,10 @@
         <v>101.42</v>
       </c>
       <c r="Q211" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="212" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A212" s="4">
         <v>42917</v>
       </c>
@@ -25086,10 +22884,10 @@
         <v>100.12</v>
       </c>
       <c r="Q212" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="213" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A213" s="4">
         <v>42948</v>
       </c>
@@ -25136,7 +22934,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A214" s="4">
         <v>42979</v>
       </c>
@@ -25183,7 +22981,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A215" s="4">
         <v>43009</v>
       </c>
@@ -25230,7 +23028,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A216" s="4">
         <v>43040</v>
       </c>
@@ -25277,7 +23075,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A217" s="4">
         <v>43070</v>
       </c>
@@ -25324,7 +23122,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A218" s="4">
         <v>43101</v>
       </c>
@@ -25368,10 +23166,10 @@
         <v>110.31</v>
       </c>
       <c r="Q218" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="219" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A219" s="4">
         <v>43132</v>
       </c>
@@ -25418,7 +23216,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A220" s="4">
         <v>43160</v>
       </c>
@@ -25465,7 +23263,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A221" s="4">
         <v>43191</v>
       </c>
@@ -25512,7 +23310,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
         <v>43221</v>
       </c>
@@ -25556,10 +23354,10 @@
         <v>112.71</v>
       </c>
       <c r="Q222" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="223" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A223" s="4">
         <v>43252</v>
       </c>
@@ -25606,7 +23404,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A224" s="4">
         <v>43282</v>
       </c>
@@ -25650,10 +23448,10 @@
         <v>114.19</v>
       </c>
       <c r="Q224" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="225" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A225" s="4">
         <v>43313</v>
       </c>
@@ -25700,7 +23498,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A226" s="4">
         <v>43344</v>
       </c>
@@ -25747,7 +23545,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A227" s="4">
         <v>43374</v>
       </c>
@@ -25794,7 +23592,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A228" s="4">
         <v>43405</v>
       </c>
@@ -25841,7 +23639,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A229" s="4">
         <v>43435</v>
       </c>
@@ -25888,7 +23686,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A230" s="4">
         <v>43466</v>
       </c>
@@ -25932,10 +23730,10 @@
         <v>112.5</v>
       </c>
       <c r="Q230" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="231" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A231" s="4">
         <v>43497</v>
       </c>
@@ -25982,7 +23780,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A232" s="4">
         <v>43525</v>
       </c>
@@ -26029,7 +23827,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
         <v>43556</v>
       </c>
@@ -26076,7 +23874,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A234" s="4">
         <v>43586</v>
       </c>
@@ -26120,10 +23918,10 @@
         <v>116.56</v>
       </c>
       <c r="Q234" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="235" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A235" s="4">
         <v>43617</v>
       </c>
@@ -26167,10 +23965,10 @@
         <v>116.32</v>
       </c>
       <c r="Q235" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="236" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A236" s="4">
         <v>43647</v>
       </c>
@@ -26217,7 +24015,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A237" s="4">
         <v>43678</v>
       </c>
@@ -26264,7 +24062,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A238" s="4">
         <v>43709</v>
       </c>
@@ -26311,7 +24109,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A239" s="4">
         <v>43739</v>
       </c>
@@ -26358,7 +24156,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A240" s="4">
         <v>43770</v>
       </c>
@@ -26405,7 +24203,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A241" s="4">
         <v>43800</v>
       </c>
@@ -26449,10 +24247,10 @@
         <v>116.69</v>
       </c>
       <c r="Q241" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="242" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A242" s="4">
         <v>43831</v>
       </c>
@@ -26499,7 +24297,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A243" s="4">
         <v>43862</v>
       </c>
@@ -26543,10 +24341,10 @@
         <v>115.04</v>
       </c>
       <c r="Q243" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="244" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
         <v>43891</v>
       </c>
@@ -26593,7 +24391,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A245" s="4">
         <v>43922</v>
       </c>
@@ -26640,7 +24438,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A246" s="4">
         <v>43952</v>
       </c>
@@ -26684,10 +24482,10 @@
         <v>103.84</v>
       </c>
       <c r="Q246" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="247" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A247" s="4">
         <v>43983</v>
       </c>
@@ -26734,7 +24532,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A248" s="4">
         <v>44013</v>
       </c>
@@ -26781,7 +24579,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A249" s="4">
         <v>44044</v>
       </c>
@@ -26828,7 +24626,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A250" s="4">
         <v>44075</v>
       </c>
@@ -26875,7 +24673,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A251" s="4">
         <v>44105</v>
       </c>
@@ -26922,7 +24720,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A252" s="4">
         <v>44136</v>
       </c>
@@ -26966,10 +24764,10 @@
         <v>106.91</v>
       </c>
       <c r="Q252" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="253" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A253" s="4">
         <v>44166</v>
       </c>
@@ -27016,7 +24814,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A254" s="4">
         <v>44197</v>
       </c>
@@ -27063,7 +24861,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
         <v>44228</v>
       </c>
@@ -27110,7 +24908,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A256" s="4">
         <v>44256</v>
       </c>
@@ -27157,7 +24955,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A257" s="4">
         <v>44287</v>
       </c>
@@ -27204,7 +25002,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="258" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A258" s="4">
         <v>44317</v>
       </c>
@@ -27248,10 +25046,10 @@
         <v>115.8</v>
       </c>
       <c r="Q258" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="259" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A259" s="4">
         <v>44348</v>
       </c>
@@ -27298,7 +25096,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A260" s="4">
         <v>44378</v>
       </c>
@@ -27345,7 +25143,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="261" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A261" s="4">
         <v>44409</v>
       </c>
@@ -27392,7 +25190,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A262" s="4">
         <v>44440</v>
       </c>
@@ -27439,7 +25237,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A263" s="4">
         <v>44470</v>
       </c>
@@ -27486,7 +25284,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A264" s="4">
         <v>44501</v>
       </c>
@@ -27530,10 +25328,10 @@
         <v>130.29</v>
       </c>
       <c r="Q264" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="265" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A265" s="4">
         <v>44531</v>
       </c>
@@ -27580,7 +25378,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
         <v>44562</v>
       </c>
@@ -27627,7 +25425,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A267" s="4">
         <v>44593</v>
       </c>
@@ -27674,7 +25472,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A268" s="4">
         <v>44621</v>
       </c>
@@ -27721,7 +25519,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A269" s="4">
         <v>44652</v>
       </c>
@@ -27768,7 +25566,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A270" s="4">
         <v>44682</v>
       </c>
@@ -27815,7 +25613,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A271" s="4">
         <v>44713</v>
       </c>
@@ -27862,7 +25660,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A272" s="4">
         <v>44743</v>
       </c>
@@ -27909,7 +25707,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="273" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A273" s="4">
         <v>44774</v>
       </c>
@@ -27953,10 +25751,10 @@
         <v>148.57</v>
       </c>
       <c r="Q273" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="274" spans="1:17" x14ac:dyDescent="0.4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="274" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A274" s="4">
         <v>44805</v>
       </c>
@@ -28003,7 +25801,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="275" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A275" s="4">
         <v>44835</v>
       </c>
@@ -28050,7 +25848,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="276" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A276" s="4">
         <v>44866</v>
       </c>
@@ -28094,10 +25892,10 @@
         <v>155</v>
       </c>
       <c r="Q276" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="277" spans="1:17" x14ac:dyDescent="0.4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="277" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
         <v>44896</v>
       </c>
@@ -28141,10 +25939,10 @@
         <v>149.49</v>
       </c>
       <c r="Q277" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="278" spans="1:17" x14ac:dyDescent="0.4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="278" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A278" s="4">
         <v>44927</v>
       </c>
@@ -28191,7 +25989,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="279" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A279" s="4">
         <v>44958</v>
       </c>
@@ -28238,7 +26036,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="280" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A280" s="4">
         <v>44986</v>
       </c>
@@ -28285,7 +26083,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="281" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A281" s="4">
         <v>45017</v>
       </c>
@@ -28329,10 +26127,10 @@
         <v>156.76</v>
       </c>
       <c r="Q281" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="282" spans="1:17" x14ac:dyDescent="0.4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="282" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A282" s="4">
         <v>45047</v>
       </c>
@@ -28376,10 +26174,10 @@
         <v>152.28</v>
       </c>
       <c r="Q282" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="283" spans="1:17" x14ac:dyDescent="0.4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="283" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A283" s="4">
         <v>45078</v>
       </c>
@@ -28426,7 +26224,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="284" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A284" s="4">
         <v>45108</v>
       </c>
@@ -28473,7 +26271,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="285" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A285" s="4">
         <v>45139</v>
       </c>
@@ -28520,7 +26318,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="286" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A286" s="4">
         <v>45170</v>
       </c>
@@ -28567,7 +26365,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="287" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A287" s="4">
         <v>45200</v>
       </c>
@@ -28611,10 +26409,10 @@
         <v>161.1</v>
       </c>
       <c r="Q287" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="288" spans="1:17" x14ac:dyDescent="0.4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="288" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
         <v>45231</v>
       </c>
@@ -28661,7 +26459,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="289" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A289" s="4">
         <v>45261</v>
       </c>
@@ -28708,7 +26506,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="290" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A290" s="4">
         <v>45292</v>
       </c>
@@ -28755,7 +26553,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="291" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A291" s="4">
         <v>45323</v>
       </c>
@@ -28802,7 +26600,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="292" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A292" s="4">
         <v>45352</v>
       </c>
@@ -28849,7 +26647,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="293" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A293" s="4">
         <v>45383</v>
       </c>
@@ -28893,10 +26691,10 @@
         <v>162.56</v>
       </c>
       <c r="Q293" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="294" spans="1:17" x14ac:dyDescent="0.4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="294" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A294" s="4">
         <v>45413</v>
       </c>
@@ -28943,7 +26741,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="295" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A295" s="4">
         <v>45444</v>
       </c>
@@ -28990,7 +26788,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="296" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A296" s="4">
         <v>45474</v>
       </c>
@@ -29037,7 +26835,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="297" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A297" s="4">
         <v>45505</v>
       </c>
@@ -29084,7 +26882,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="298" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A298" s="4">
         <v>45536</v>
       </c>
@@ -29131,7 +26929,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="299" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
         <v>45566</v>
       </c>
@@ -29175,10 +26973,10 @@
         <v>158</v>
       </c>
       <c r="Q299" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="300" spans="1:17" x14ac:dyDescent="0.4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="300" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A300" s="4">
         <v>45597</v>
       </c>
@@ -29225,7 +27023,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="301" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A301" s="4">
         <v>45627</v>
       </c>
@@ -29269,10 +27067,10 @@
         <v>159.58000000000001</v>
       </c>
       <c r="Q301" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="302" spans="1:17" x14ac:dyDescent="0.4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="302" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A302" s="4">
         <v>45658</v>
       </c>
@@ -29319,7 +27117,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="303" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A303" s="4">
         <v>45689</v>
       </c>
@@ -29363,10 +27161,10 @@
         <v>154.96</v>
       </c>
       <c r="Q303" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="304" spans="1:17" x14ac:dyDescent="0.4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="304" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A304" s="4">
         <v>45717</v>
       </c>
@@ -29410,10 +27208,10 @@
         <v>152.77000000000001</v>
       </c>
       <c r="Q304" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="305" spans="1:17" x14ac:dyDescent="0.4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="305" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A305" s="4">
         <v>45748</v>
       </c>
@@ -29460,7 +27258,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="306" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A306" s="4">
         <v>45778</v>
       </c>
@@ -29507,7 +27305,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="307" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A307" s="4">
         <v>45809</v>
       </c>
@@ -29554,7 +27352,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="308" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A308" s="4">
         <v>45839</v>
       </c>
@@ -29601,7 +27399,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="309" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A309" s="4">
         <v>45870</v>
       </c>
@@ -29648,7 +27446,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="310" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
         <v>45901</v>
       </c>
@@ -29692,10 +27490,10 @@
         <v>149.9</v>
       </c>
       <c r="Q310" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="311" spans="1:17" x14ac:dyDescent="0.4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="311" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A311" s="4">
         <v>45931</v>
       </c>
@@ -29739,10 +27537,10 @@
         <v>149.30000000000001</v>
       </c>
       <c r="Q311" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="312" spans="1:17" x14ac:dyDescent="0.4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="312" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A312" s="4">
         <v>45962</v>
       </c>
@@ -29789,7 +27587,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="313" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A313" s="4">
         <v>45992</v>
       </c>
